--- a/Stock_OneClick/history/scan_result_20260604_101717.xlsx
+++ b/Stock_OneClick/history/scan_result_20260604_101717.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q278"/>
+  <dimension ref="A1:Q277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -671,24 +671,6 @@
       <c r="J3" t="n">
         <v>16.715</v>
       </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-06-04; 相对D0=3.69%; 本次触发=2026-06-04(预警买入); 历史重复2次; 重复日期=2026-05-27, 2026-06-04</t>
@@ -740,24 +722,6 @@
       <c r="J4" t="n">
         <v>51.52</v>
       </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>D0=50.66; 最新=2026-06-04; 相对D0=1.70%; 本次触发=2026-06-04(正式买入 | 预警买入); 历史重复4次; 重复日期=2026-05-27, 2026-06-01, 2026-06-03, 2026-06-04</t>
@@ -809,24 +773,12 @@
       <c r="J5" s="5" t="n">
         <v>14.315</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-06-04; 相对D0=9.95%; 本次触发=2026-06-04(预警买入); 历史重复4次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02, 2026-06-04</t>
@@ -878,24 +830,6 @@
       <c r="J6" t="n">
         <v>397.02</v>
       </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>D0=388.47; 最新=2026-06-04; 相对D0=2.20%; 本次触发=2026-06-04(正式买入 | 预警买入); 历史重复3次; 重复日期=2026-05-27, 2026-06-03, 2026-06-04</t>
@@ -947,24 +881,12 @@
       <c r="J7" s="5" t="n">
         <v>372.22</v>
       </c>
-      <c r="K7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
       <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>D0=388.88; 最新=2026-06-04; 相对D0=-4.28%; 本次触发=2026-06-04(预警买入); 历史重复2次; 重复日期=2026-05-28, 2026-06-04</t>
@@ -1016,24 +938,6 @@
       <c r="J8" t="n">
         <v>16.985</v>
       </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>D0=15.98; 最新=2026-06-04; 相对D0=6.29%; 本次触发=2026-06-04(正式买入); 历史重复1次; 重复日期=2026-06-04</t>
@@ -1085,24 +989,6 @@
       <c r="J9" t="n">
         <v>86.62</v>
       </c>
-      <c r="K9" t="n">
-        <v/>
-      </c>
-      <c r="L9" t="n">
-        <v/>
-      </c>
-      <c r="M9" t="n">
-        <v/>
-      </c>
-      <c r="N9" t="n">
-        <v/>
-      </c>
-      <c r="O9" t="n">
-        <v/>
-      </c>
-      <c r="P9" t="n">
-        <v/>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>D0=76.23; 最新=2026-06-04; 相对D0=13.63%; 本次触发=2026-06-04(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-28, 2026-06-04</t>
@@ -1154,24 +1040,12 @@
       <c r="J10" s="5" t="n">
         <v>120.94</v>
       </c>
-      <c r="K10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
       <c r="Q10" s="5" t="inlineStr">
         <is>
           <t>D0=102.12; 最新=2026-06-04; 相对D0=18.43%; 本次触发=2026-06-04(预警买入); 历史重复1次; 重复日期=2026-06-04</t>
@@ -1223,24 +1097,6 @@
       <c r="J11" t="n">
         <v>293.63</v>
       </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>D0=290.01; 最新=2026-06-04; 相对D0=1.25%; 本次触发=2026-06-04(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-06-02, 2026-06-04</t>
@@ -1292,24 +1148,6 @@
       <c r="J12" t="n">
         <v>66.75</v>
       </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>D0=67.38; 最新=2026-06-04; 相对D0=-0.93%; 本次触发=2026-06-04(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-06-02, 2026-06-04</t>
@@ -1361,24 +1199,12 @@
       <c r="J13" s="5" t="n">
         <v>260.31</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>D0=259.21; 最新=2026-06-04; 相对D0=0.42%; 本次触发=2026-06-04(预警买入); 历史重复1次; 重复日期=2026-06-04</t>
@@ -1430,24 +1256,12 @@
       <c r="J14" s="5" t="n">
         <v>219.28</v>
       </c>
-      <c r="K14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>D0=211.14; 最新=2026-06-04; 相对D0=3.86%; 本次触发=2026-06-04(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-06-01, 2026-06-04</t>
@@ -1499,24 +1313,6 @@
       <c r="J15" t="n">
         <v>52.135</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=51.58; 最新=2026-06-04; 相对D0=1.08%; 本次触发=2026-06-04(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-06-02, 2026-06-04</t>
@@ -1568,27 +1364,9 @@
       <c r="J16" t="n">
         <v>323</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>D0=320.41; 最新=2026-06-04; 相对D0=0.81%; 本次触发=2026-06-04(正式买入 | 第一买入点 | 预警买入); 历史重复1次; 重复日期=2026-06-04</t>
+          <t>D0=320.41; 最新=2026-06-04; 相对D0=0.81%; 本次触发=2026-06-04(正式买入 | 第一观察点 | 预警买入); 历史重复1次; 重复日期=2026-06-04</t>
         </is>
       </c>
     </row>
@@ -1637,24 +1415,6 @@
       <c r="J17" t="n">
         <v>222.81</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=229.00; 最新=2026-06-04; 相对D0=-2.70%; 本次触发=2026-06-04(正式买入 | 预警买入); 历史重复1次; 重复日期=2026-06-04</t>
@@ -1706,24 +1466,6 @@
       <c r="J18" t="n">
         <v>117.54</v>
       </c>
-      <c r="K18" t="n">
-        <v/>
-      </c>
-      <c r="L18" t="n">
-        <v/>
-      </c>
-      <c r="M18" t="n">
-        <v/>
-      </c>
-      <c r="N18" t="n">
-        <v/>
-      </c>
-      <c r="O18" t="n">
-        <v/>
-      </c>
-      <c r="P18" t="n">
-        <v/>
-      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>D0=116.60; 最新=2026-06-04; 相对D0=0.81%; 本次触发=2026-06-04(正式买入); 历史重复1次; 重复日期=2026-06-04</t>
@@ -1775,24 +1517,6 @@
       <c r="J19" t="n">
         <v>80.45</v>
       </c>
-      <c r="K19" t="n">
-        <v/>
-      </c>
-      <c r="L19" t="n">
-        <v/>
-      </c>
-      <c r="M19" t="n">
-        <v/>
-      </c>
-      <c r="N19" t="n">
-        <v/>
-      </c>
-      <c r="O19" t="n">
-        <v/>
-      </c>
-      <c r="P19" t="n">
-        <v/>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>D0=80.14; 最新=2026-06-04; 相对D0=0.39%; 本次触发=2026-06-04(正式买入); 历史重复1次; 重复日期=2026-06-04</t>
@@ -1844,24 +1568,12 @@
       <c r="J20" s="5" t="n">
         <v>260.31</v>
       </c>
-      <c r="K20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O20" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P20" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
+      <c r="N20" s="5" t="n"/>
+      <c r="O20" s="5" t="n"/>
+      <c r="P20" s="5" t="n"/>
       <c r="Q20" s="5" t="inlineStr">
         <is>
           <t>D0=260.31; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -1913,27 +1625,9 @@
       <c r="J21" t="n">
         <v>323</v>
       </c>
-      <c r="K21" t="n">
-        <v/>
-      </c>
-      <c r="L21" t="n">
-        <v/>
-      </c>
-      <c r="M21" t="n">
-        <v/>
-      </c>
-      <c r="N21" t="n">
-        <v/>
-      </c>
-      <c r="O21" t="n">
-        <v/>
-      </c>
-      <c r="P21" t="n">
-        <v/>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>D0=323.00; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 第一买入点 | 预警买入)</t>
+          <t>D0=323.00; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 第一观察点 | 预警买入)</t>
         </is>
       </c>
     </row>
@@ -1982,24 +1676,6 @@
       <c r="J22" t="n">
         <v>293.63</v>
       </c>
-      <c r="K22" t="n">
-        <v/>
-      </c>
-      <c r="L22" t="n">
-        <v/>
-      </c>
-      <c r="M22" t="n">
-        <v/>
-      </c>
-      <c r="N22" t="n">
-        <v/>
-      </c>
-      <c r="O22" t="n">
-        <v/>
-      </c>
-      <c r="P22" t="n">
-        <v/>
-      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>D0=293.63; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 预警买入)</t>
@@ -2051,24 +1727,6 @@
       <c r="J23" t="n">
         <v>117.54</v>
       </c>
-      <c r="K23" t="n">
-        <v/>
-      </c>
-      <c r="L23" t="n">
-        <v/>
-      </c>
-      <c r="M23" t="n">
-        <v/>
-      </c>
-      <c r="N23" t="n">
-        <v/>
-      </c>
-      <c r="O23" t="n">
-        <v/>
-      </c>
-      <c r="P23" t="n">
-        <v/>
-      </c>
       <c r="Q23" t="inlineStr">
         <is>
           <t>D0=117.54; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入)</t>
@@ -2120,24 +1778,6 @@
       <c r="J24" t="n">
         <v>16.715</v>
       </c>
-      <c r="K24" t="n">
-        <v/>
-      </c>
-      <c r="L24" t="n">
-        <v/>
-      </c>
-      <c r="M24" t="n">
-        <v/>
-      </c>
-      <c r="N24" t="n">
-        <v/>
-      </c>
-      <c r="O24" t="n">
-        <v/>
-      </c>
-      <c r="P24" t="n">
-        <v/>
-      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>D0=16.71; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -2189,24 +1829,6 @@
       <c r="J25" t="n">
         <v>222.81</v>
       </c>
-      <c r="K25" t="n">
-        <v/>
-      </c>
-      <c r="L25" t="n">
-        <v/>
-      </c>
-      <c r="M25" t="n">
-        <v/>
-      </c>
-      <c r="N25" t="n">
-        <v/>
-      </c>
-      <c r="O25" t="n">
-        <v/>
-      </c>
-      <c r="P25" t="n">
-        <v/>
-      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>D0=222.81; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 预警买入)</t>
@@ -2258,24 +1880,6 @@
       <c r="J26" t="n">
         <v>66.75</v>
       </c>
-      <c r="K26" t="n">
-        <v/>
-      </c>
-      <c r="L26" t="n">
-        <v/>
-      </c>
-      <c r="M26" t="n">
-        <v/>
-      </c>
-      <c r="N26" t="n">
-        <v/>
-      </c>
-      <c r="O26" t="n">
-        <v/>
-      </c>
-      <c r="P26" t="n">
-        <v/>
-      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>D0=66.75; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 预警买入)</t>
@@ -2327,24 +1931,12 @@
       <c r="J27" s="5" t="n">
         <v>372.22</v>
       </c>
-      <c r="K27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O27" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P27" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
       <c r="Q27" s="5" t="inlineStr">
         <is>
           <t>D0=372.22; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -2396,24 +1988,6 @@
       <c r="J28" t="n">
         <v>82.855</v>
       </c>
-      <c r="K28" t="n">
-        <v/>
-      </c>
-      <c r="L28" t="n">
-        <v/>
-      </c>
-      <c r="M28" t="n">
-        <v/>
-      </c>
-      <c r="N28" t="n">
-        <v/>
-      </c>
-      <c r="O28" t="n">
-        <v/>
-      </c>
-      <c r="P28" t="n">
-        <v/>
-      </c>
       <c r="Q28" t="inlineStr">
         <is>
           <t>D0=82.86; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 预警买入)</t>
@@ -2465,24 +2039,6 @@
       <c r="J29" t="n">
         <v>86.62</v>
       </c>
-      <c r="K29" t="n">
-        <v/>
-      </c>
-      <c r="L29" t="n">
-        <v/>
-      </c>
-      <c r="M29" t="n">
-        <v/>
-      </c>
-      <c r="N29" t="n">
-        <v/>
-      </c>
-      <c r="O29" t="n">
-        <v/>
-      </c>
-      <c r="P29" t="n">
-        <v/>
-      </c>
       <c r="Q29" t="inlineStr">
         <is>
           <t>D0=86.62; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 预警买入)</t>
@@ -2534,24 +2090,6 @@
       <c r="J30" t="n">
         <v>51.52</v>
       </c>
-      <c r="K30" t="n">
-        <v/>
-      </c>
-      <c r="L30" t="n">
-        <v/>
-      </c>
-      <c r="M30" t="n">
-        <v/>
-      </c>
-      <c r="N30" t="n">
-        <v/>
-      </c>
-      <c r="O30" t="n">
-        <v/>
-      </c>
-      <c r="P30" t="n">
-        <v/>
-      </c>
       <c r="Q30" t="inlineStr">
         <is>
           <t>D0=51.52; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 预警买入)</t>
@@ -2603,24 +2141,6 @@
       <c r="J31" t="n">
         <v>52.29</v>
       </c>
-      <c r="K31" t="n">
-        <v/>
-      </c>
-      <c r="L31" t="n">
-        <v/>
-      </c>
-      <c r="M31" t="n">
-        <v/>
-      </c>
-      <c r="N31" t="n">
-        <v/>
-      </c>
-      <c r="O31" t="n">
-        <v/>
-      </c>
-      <c r="P31" t="n">
-        <v/>
-      </c>
       <c r="Q31" t="inlineStr">
         <is>
           <t>D0=52.29; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -2672,24 +2192,6 @@
       <c r="J32" t="n">
         <v>80.45</v>
       </c>
-      <c r="K32" t="n">
-        <v/>
-      </c>
-      <c r="L32" t="n">
-        <v/>
-      </c>
-      <c r="M32" t="n">
-        <v/>
-      </c>
-      <c r="N32" t="n">
-        <v/>
-      </c>
-      <c r="O32" t="n">
-        <v/>
-      </c>
-      <c r="P32" t="n">
-        <v/>
-      </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>D0=80.45; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入)</t>
@@ -2741,24 +2243,12 @@
       <c r="J33" s="5" t="n">
         <v>120.94</v>
       </c>
-      <c r="K33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="inlineStr">
         <is>
           <t>D0=120.94; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -2810,24 +2300,12 @@
       <c r="J34" s="5" t="n">
         <v>219.28</v>
       </c>
-      <c r="K34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+      <c r="P34" s="5" t="n"/>
       <c r="Q34" s="5" t="inlineStr">
         <is>
           <t>D0=219.28; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 预警买入)</t>
@@ -2879,24 +2357,12 @@
       <c r="J35" s="5" t="n">
         <v>244.7</v>
       </c>
-      <c r="K35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P35" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
+      <c r="P35" s="5" t="n"/>
       <c r="Q35" s="5" t="inlineStr">
         <is>
           <t>D0=244.70; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -2948,24 +2414,6 @@
       <c r="J36" t="n">
         <v>16.985</v>
       </c>
-      <c r="K36" t="n">
-        <v/>
-      </c>
-      <c r="L36" t="n">
-        <v/>
-      </c>
-      <c r="M36" t="n">
-        <v/>
-      </c>
-      <c r="N36" t="n">
-        <v/>
-      </c>
-      <c r="O36" t="n">
-        <v/>
-      </c>
-      <c r="P36" t="n">
-        <v/>
-      </c>
       <c r="Q36" t="inlineStr">
         <is>
           <t>D0=16.98; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入)</t>
@@ -3017,24 +2465,12 @@
       <c r="J37" s="5" t="n">
         <v>14.315</v>
       </c>
-      <c r="K37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P37" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
       <c r="Q37" s="5" t="inlineStr">
         <is>
           <t>D0=14.31; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(预警买入)</t>
@@ -3086,24 +2522,6 @@
       <c r="J38" t="n">
         <v>397.02</v>
       </c>
-      <c r="K38" t="n">
-        <v/>
-      </c>
-      <c r="L38" t="n">
-        <v/>
-      </c>
-      <c r="M38" t="n">
-        <v/>
-      </c>
-      <c r="N38" t="n">
-        <v/>
-      </c>
-      <c r="O38" t="n">
-        <v/>
-      </c>
-      <c r="P38" t="n">
-        <v/>
-      </c>
       <c r="Q38" t="inlineStr">
         <is>
           <t>D0=397.02; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 预警买入)</t>
@@ -3155,24 +2573,6 @@
       <c r="J39" t="n">
         <v>52.135</v>
       </c>
-      <c r="K39" t="n">
-        <v/>
-      </c>
-      <c r="L39" t="n">
-        <v/>
-      </c>
-      <c r="M39" t="n">
-        <v/>
-      </c>
-      <c r="N39" t="n">
-        <v/>
-      </c>
-      <c r="O39" t="n">
-        <v/>
-      </c>
-      <c r="P39" t="n">
-        <v/>
-      </c>
       <c r="Q39" t="inlineStr">
         <is>
           <t>D0=52.13; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式买入 | 预警买入)</t>
@@ -3224,24 +2624,6 @@
       <c r="J40" t="n">
         <v>198.7336</v>
       </c>
-      <c r="K40" t="n">
-        <v/>
-      </c>
-      <c r="L40" t="n">
-        <v/>
-      </c>
-      <c r="M40" t="n">
-        <v/>
-      </c>
-      <c r="N40" t="n">
-        <v/>
-      </c>
-      <c r="O40" t="n">
-        <v/>
-      </c>
-      <c r="P40" t="n">
-        <v/>
-      </c>
       <c r="Q40" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-06-04; 相对D0=9.50%; 历史重复3次; 重复日期=2026-05-27, 2026-06-01, 2026-06-03</t>
@@ -3293,24 +2675,12 @@
       <c r="J41" s="5" t="n">
         <v>189.52</v>
       </c>
-      <c r="K41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P41" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="n"/>
+      <c r="O41" s="5" t="n"/>
+      <c r="P41" s="5" t="n"/>
       <c r="Q41" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-06-04; 相对D0=-6.60%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -3362,24 +2732,12 @@
       <c r="J42" s="5" t="n">
         <v>181.05</v>
       </c>
-      <c r="K42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P42" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="n"/>
+      <c r="O42" s="5" t="n"/>
+      <c r="P42" s="5" t="n"/>
       <c r="Q42" s="5" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-06-04; 相对D0=8.17%; 历史重复3次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02</t>
@@ -3431,24 +2789,12 @@
       <c r="J43" s="5" t="n">
         <v>264.2</v>
       </c>
-      <c r="K43" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L43" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M43" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N43" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O43" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P43" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K43" s="5" t="n"/>
+      <c r="L43" s="5" t="n"/>
+      <c r="M43" s="5" t="n"/>
+      <c r="N43" s="5" t="n"/>
+      <c r="O43" s="5" t="n"/>
+      <c r="P43" s="5" t="n"/>
       <c r="Q43" s="5" t="inlineStr">
         <is>
           <t>D0=294.07; 最新=2026-06-04; 相对D0=-10.16%; 历史重复1次; 重复日期=2026-05-29</t>
@@ -3500,24 +2846,12 @@
       <c r="J44" s="5" t="n">
         <v>56.59</v>
       </c>
-      <c r="K44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O44" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P44" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="5" t="n"/>
+      <c r="M44" s="5" t="n"/>
+      <c r="N44" s="5" t="n"/>
+      <c r="O44" s="5" t="n"/>
+      <c r="P44" s="5" t="n"/>
       <c r="Q44" s="5" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-06-04; 相对D0=21.62%</t>
@@ -3569,24 +2903,12 @@
       <c r="J45" s="5" t="n">
         <v>189.055</v>
       </c>
-      <c r="K45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P45" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="5" t="n"/>
       <c r="Q45" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-06-04; 相对D0=4.99%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -3638,24 +2960,12 @@
       <c r="J46" s="5" t="n">
         <v>47.42</v>
       </c>
-      <c r="K46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P46" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="n"/>
+      <c r="O46" s="5" t="n"/>
+      <c r="P46" s="5" t="n"/>
       <c r="Q46" s="5" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-06-04; 相对D0=-1.45%; 历史重复3次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02</t>
@@ -3707,24 +3017,12 @@
       <c r="J47" s="5" t="n">
         <v>140.975</v>
       </c>
-      <c r="K47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O47" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P47" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K47" s="5" t="n"/>
+      <c r="L47" s="5" t="n"/>
+      <c r="M47" s="5" t="n"/>
+      <c r="N47" s="5" t="n"/>
+      <c r="O47" s="5" t="n"/>
+      <c r="P47" s="5" t="n"/>
       <c r="Q47" s="5" t="inlineStr">
         <is>
           <t>D0=135.28; 最新=2026-06-04; 相对D0=4.21%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -3776,24 +3074,12 @@
       <c r="J48" s="5" t="n">
         <v>140.775</v>
       </c>
-      <c r="K48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O48" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P48" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K48" s="5" t="n"/>
+      <c r="L48" s="5" t="n"/>
+      <c r="M48" s="5" t="n"/>
+      <c r="N48" s="5" t="n"/>
+      <c r="O48" s="5" t="n"/>
+      <c r="P48" s="5" t="n"/>
       <c r="Q48" s="5" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-06-04; 相对D0=-0.32%; 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -3845,24 +3131,6 @@
       <c r="J49" t="n">
         <v>417.55</v>
       </c>
-      <c r="K49" t="n">
-        <v/>
-      </c>
-      <c r="L49" t="n">
-        <v/>
-      </c>
-      <c r="M49" t="n">
-        <v/>
-      </c>
-      <c r="N49" t="n">
-        <v/>
-      </c>
-      <c r="O49" t="n">
-        <v/>
-      </c>
-      <c r="P49" t="n">
-        <v/>
-      </c>
       <c r="Q49" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-06-04; 相对D0=6.69%; 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -3914,24 +3182,6 @@
       <c r="J50" t="n">
         <v>962.25</v>
       </c>
-      <c r="K50" t="n">
-        <v/>
-      </c>
-      <c r="L50" t="n">
-        <v/>
-      </c>
-      <c r="M50" t="n">
-        <v/>
-      </c>
-      <c r="N50" t="n">
-        <v/>
-      </c>
-      <c r="O50" t="n">
-        <v/>
-      </c>
-      <c r="P50" t="n">
-        <v/>
-      </c>
       <c r="Q50" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-06-04; 相对D0=-7.36%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -3983,24 +3233,12 @@
       <c r="J51" s="5" t="n">
         <v>185</v>
       </c>
-      <c r="K51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P51" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="n"/>
+      <c r="O51" s="5" t="n"/>
+      <c r="P51" s="5" t="n"/>
       <c r="Q51" s="5" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-06-04; 相对D0=3.14%; 历史重复3次; 重复日期=2026-05-26, 2026-05-28, 2026-06-01</t>
@@ -4052,24 +3290,12 @@
       <c r="J52" s="5" t="n">
         <v>379.68</v>
       </c>
-      <c r="K52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P52" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="n"/>
+      <c r="O52" s="5" t="n"/>
+      <c r="P52" s="5" t="n"/>
       <c r="Q52" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-06-04; 相对D0=16.42%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -4121,24 +3347,12 @@
       <c r="J53" s="5" t="n">
         <v>629.355</v>
       </c>
-      <c r="K53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O53" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P53" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K53" s="5" t="n"/>
+      <c r="L53" s="5" t="n"/>
+      <c r="M53" s="5" t="n"/>
+      <c r="N53" s="5" t="n"/>
+      <c r="O53" s="5" t="n"/>
+      <c r="P53" s="5" t="n"/>
       <c r="Q53" s="5" t="inlineStr">
         <is>
           <t>D0=610.26; 最新=2026-06-04; 相对D0=3.13%; 历史重复2次; 重复日期=2026-05-26, 2026-06-03</t>
@@ -4190,24 +3404,6 @@
       <c r="J54" t="n">
         <v>22.66</v>
       </c>
-      <c r="K54" t="n">
-        <v/>
-      </c>
-      <c r="L54" t="n">
-        <v/>
-      </c>
-      <c r="M54" t="n">
-        <v/>
-      </c>
-      <c r="N54" t="n">
-        <v/>
-      </c>
-      <c r="O54" t="n">
-        <v/>
-      </c>
-      <c r="P54" t="n">
-        <v/>
-      </c>
       <c r="Q54" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-06-04; 相对D0=0.67%; 历史重复3次; 重复日期=2026-05-26, 2026-06-02, 2026-06-03</t>
@@ -4259,24 +3455,12 @@
       <c r="J55" s="5" t="n">
         <v>25.705</v>
       </c>
-      <c r="K55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O55" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P55" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K55" s="5" t="n"/>
+      <c r="L55" s="5" t="n"/>
+      <c r="M55" s="5" t="n"/>
+      <c r="N55" s="5" t="n"/>
+      <c r="O55" s="5" t="n"/>
+      <c r="P55" s="5" t="n"/>
       <c r="Q55" s="5" t="inlineStr">
         <is>
           <t>D0=26.73; 最新=2026-06-04; 相对D0=-3.83%</t>
@@ -4328,24 +3512,6 @@
       <c r="J56" t="n">
         <v>132.615</v>
       </c>
-      <c r="K56" t="n">
-        <v/>
-      </c>
-      <c r="L56" t="n">
-        <v/>
-      </c>
-      <c r="M56" t="n">
-        <v/>
-      </c>
-      <c r="N56" t="n">
-        <v/>
-      </c>
-      <c r="O56" t="n">
-        <v/>
-      </c>
-      <c r="P56" t="n">
-        <v/>
-      </c>
       <c r="Q56" t="inlineStr">
         <is>
           <t>D0=137.65; 最新=2026-06-04; 相对D0=-3.66%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -4397,24 +3563,6 @@
       <c r="J57" t="n">
         <v>262.29</v>
       </c>
-      <c r="K57" t="n">
-        <v/>
-      </c>
-      <c r="L57" t="n">
-        <v/>
-      </c>
-      <c r="M57" t="n">
-        <v/>
-      </c>
-      <c r="N57" t="n">
-        <v/>
-      </c>
-      <c r="O57" t="n">
-        <v/>
-      </c>
-      <c r="P57" t="n">
-        <v/>
-      </c>
       <c r="Q57" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-06-04; 相对D0=13.06%</t>
@@ -4466,24 +3614,6 @@
       <c r="J58" t="n">
         <v>148.525</v>
       </c>
-      <c r="K58" t="n">
-        <v/>
-      </c>
-      <c r="L58" t="n">
-        <v/>
-      </c>
-      <c r="M58" t="n">
-        <v/>
-      </c>
-      <c r="N58" t="n">
-        <v/>
-      </c>
-      <c r="O58" t="n">
-        <v/>
-      </c>
-      <c r="P58" t="n">
-        <v/>
-      </c>
       <c r="Q58" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-06-04; 相对D0=13.81%; 历史重复1次; 重复日期=2026-06-03</t>
@@ -4535,24 +3665,12 @@
       <c r="J59" s="5" t="n">
         <v>276.586</v>
       </c>
-      <c r="K59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P59" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K59" s="5" t="n"/>
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="n"/>
+      <c r="O59" s="5" t="n"/>
+      <c r="P59" s="5" t="n"/>
       <c r="Q59" s="5" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-06-04; 相对D0=5.47%; 历史重复3次; 重复日期=2026-05-26, 2026-05-27, 2026-06-02</t>
@@ -4604,24 +3722,12 @@
       <c r="J60" s="5" t="n">
         <v>58.49</v>
       </c>
-      <c r="K60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O60" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P60" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K60" s="5" t="n"/>
+      <c r="L60" s="5" t="n"/>
+      <c r="M60" s="5" t="n"/>
+      <c r="N60" s="5" t="n"/>
+      <c r="O60" s="5" t="n"/>
+      <c r="P60" s="5" t="n"/>
       <c r="Q60" s="5" t="inlineStr">
         <is>
           <t>D0=58.81; 最新=2026-06-04; 相对D0=-0.54%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -4673,24 +3779,6 @@
       <c r="J61" t="n">
         <v>57.47</v>
       </c>
-      <c r="K61" t="n">
-        <v/>
-      </c>
-      <c r="L61" t="n">
-        <v/>
-      </c>
-      <c r="M61" t="n">
-        <v/>
-      </c>
-      <c r="N61" t="n">
-        <v/>
-      </c>
-      <c r="O61" t="n">
-        <v/>
-      </c>
-      <c r="P61" t="n">
-        <v/>
-      </c>
       <c r="Q61" t="inlineStr">
         <is>
           <t>D0=54.94; 最新=2026-06-04; 相对D0=4.61%; 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -4742,24 +3830,6 @@
       <c r="J62" t="n">
         <v>84.91500000000001</v>
       </c>
-      <c r="K62" t="n">
-        <v/>
-      </c>
-      <c r="L62" t="n">
-        <v/>
-      </c>
-      <c r="M62" t="n">
-        <v/>
-      </c>
-      <c r="N62" t="n">
-        <v/>
-      </c>
-      <c r="O62" t="n">
-        <v/>
-      </c>
-      <c r="P62" t="n">
-        <v/>
-      </c>
       <c r="Q62" t="inlineStr">
         <is>
           <t>D0=81.76; 最新=2026-06-04; 相对D0=3.86%; 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -4811,24 +3881,12 @@
       <c r="J63" s="5" t="n">
         <v>101.165</v>
       </c>
-      <c r="K63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P63" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K63" s="5" t="n"/>
+      <c r="L63" s="5" t="n"/>
+      <c r="M63" s="5" t="n"/>
+      <c r="N63" s="5" t="n"/>
+      <c r="O63" s="5" t="n"/>
+      <c r="P63" s="5" t="n"/>
       <c r="Q63" s="5" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-06-04; 相对D0=18.43%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -4880,24 +3938,12 @@
       <c r="J64" s="5" t="n">
         <v>419.4</v>
       </c>
-      <c r="K64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P64" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K64" s="5" t="n"/>
+      <c r="L64" s="5" t="n"/>
+      <c r="M64" s="5" t="n"/>
+      <c r="N64" s="5" t="n"/>
+      <c r="O64" s="5" t="n"/>
+      <c r="P64" s="5" t="n"/>
       <c r="Q64" s="5" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-06-04; 相对D0=-1.55%</t>
@@ -4949,24 +3995,6 @@
       <c r="J65" t="n">
         <v>152.85</v>
       </c>
-      <c r="K65" t="n">
-        <v/>
-      </c>
-      <c r="L65" t="n">
-        <v/>
-      </c>
-      <c r="M65" t="n">
-        <v/>
-      </c>
-      <c r="N65" t="n">
-        <v/>
-      </c>
-      <c r="O65" t="n">
-        <v/>
-      </c>
-      <c r="P65" t="n">
-        <v/>
-      </c>
       <c r="Q65" t="inlineStr">
         <is>
           <t>D0=156.27; 最新=2026-06-04; 相对D0=-2.19%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -5018,24 +4046,6 @@
       <c r="J66" t="n">
         <v>51.635</v>
       </c>
-      <c r="K66" t="n">
-        <v/>
-      </c>
-      <c r="L66" t="n">
-        <v/>
-      </c>
-      <c r="M66" t="n">
-        <v/>
-      </c>
-      <c r="N66" t="n">
-        <v/>
-      </c>
-      <c r="O66" t="n">
-        <v/>
-      </c>
-      <c r="P66" t="n">
-        <v/>
-      </c>
       <c r="Q66" t="inlineStr">
         <is>
           <t>D0=50.29; 最新=2026-06-04; 相对D0=2.67%; 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -5087,24 +4097,12 @@
       <c r="J67" s="5" t="n">
         <v>75.23999999999999</v>
       </c>
-      <c r="K67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O67" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P67" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K67" s="5" t="n"/>
+      <c r="L67" s="5" t="n"/>
+      <c r="M67" s="5" t="n"/>
+      <c r="N67" s="5" t="n"/>
+      <c r="O67" s="5" t="n"/>
+      <c r="P67" s="5" t="n"/>
       <c r="Q67" s="5" t="inlineStr">
         <is>
           <t>D0=73.46; 最新=2026-06-04; 相对D0=2.42%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -5156,24 +4154,6 @@
       <c r="J68" t="n">
         <v>417.92</v>
       </c>
-      <c r="K68" t="n">
-        <v/>
-      </c>
-      <c r="L68" t="n">
-        <v/>
-      </c>
-      <c r="M68" t="n">
-        <v/>
-      </c>
-      <c r="N68" t="n">
-        <v/>
-      </c>
-      <c r="O68" t="n">
-        <v/>
-      </c>
-      <c r="P68" t="n">
-        <v/>
-      </c>
       <c r="Q68" t="inlineStr">
         <is>
           <t>D0=422.01; 最新=2026-06-04; 相对D0=-0.97%</t>
@@ -5225,24 +4205,6 @@
       <c r="J69" t="n">
         <v>88.44</v>
       </c>
-      <c r="K69" t="n">
-        <v/>
-      </c>
-      <c r="L69" t="n">
-        <v/>
-      </c>
-      <c r="M69" t="n">
-        <v/>
-      </c>
-      <c r="N69" t="n">
-        <v/>
-      </c>
-      <c r="O69" t="n">
-        <v/>
-      </c>
-      <c r="P69" t="n">
-        <v/>
-      </c>
       <c r="Q69" t="inlineStr">
         <is>
           <t>D0=86.49; 最新=2026-06-04; 相对D0=2.25%</t>
@@ -5294,24 +4256,12 @@
       <c r="J70" s="5" t="n">
         <v>189.52</v>
       </c>
-      <c r="K70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P70" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K70" s="5" t="n"/>
+      <c r="L70" s="5" t="n"/>
+      <c r="M70" s="5" t="n"/>
+      <c r="N70" s="5" t="n"/>
+      <c r="O70" s="5" t="n"/>
+      <c r="P70" s="5" t="n"/>
       <c r="Q70" s="5" t="inlineStr">
         <is>
           <t>D0=204.38; 最新=2026-06-04; 相对D0=-7.27%</t>
@@ -5363,24 +4313,12 @@
       <c r="J71" s="5" t="n">
         <v>181.05</v>
       </c>
-      <c r="K71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P71" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K71" s="5" t="n"/>
+      <c r="L71" s="5" t="n"/>
+      <c r="M71" s="5" t="n"/>
+      <c r="N71" s="5" t="n"/>
+      <c r="O71" s="5" t="n"/>
+      <c r="P71" s="5" t="n"/>
       <c r="Q71" s="5" t="inlineStr">
         <is>
           <t>D0=174.73; 最新=2026-06-04; 相对D0=3.62%</t>
@@ -5432,24 +4370,12 @@
       <c r="J72" s="5" t="n">
         <v>114.45</v>
       </c>
-      <c r="K72" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M72" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N72" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O72" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P72" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K72" s="5" t="n"/>
+      <c r="L72" s="5" t="n"/>
+      <c r="M72" s="5" t="n"/>
+      <c r="N72" s="5" t="n"/>
+      <c r="O72" s="5" t="n"/>
+      <c r="P72" s="5" t="n"/>
       <c r="Q72" s="5" t="inlineStr">
         <is>
           <t>D0=108.17; 最新=2026-06-04; 相对D0=5.81%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -5501,24 +4427,6 @@
       <c r="J73" t="n">
         <v>108.39</v>
       </c>
-      <c r="K73" t="n">
-        <v/>
-      </c>
-      <c r="L73" t="n">
-        <v/>
-      </c>
-      <c r="M73" t="n">
-        <v/>
-      </c>
-      <c r="N73" t="n">
-        <v/>
-      </c>
-      <c r="O73" t="n">
-        <v/>
-      </c>
-      <c r="P73" t="n">
-        <v/>
-      </c>
       <c r="Q73" t="inlineStr">
         <is>
           <t>D0=105.89; 最新=2026-06-04; 相对D0=2.36%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -5570,24 +4478,12 @@
       <c r="J74" s="5" t="n">
         <v>47.42</v>
       </c>
-      <c r="K74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P74" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K74" s="5" t="n"/>
+      <c r="L74" s="5" t="n"/>
+      <c r="M74" s="5" t="n"/>
+      <c r="N74" s="5" t="n"/>
+      <c r="O74" s="5" t="n"/>
+      <c r="P74" s="5" t="n"/>
       <c r="Q74" s="5" t="inlineStr">
         <is>
           <t>D0=49.46; 最新=2026-06-04; 相对D0=-4.12%</t>
@@ -5639,24 +4535,6 @@
       <c r="J75" t="n">
         <v>417.55</v>
       </c>
-      <c r="K75" t="n">
-        <v/>
-      </c>
-      <c r="L75" t="n">
-        <v/>
-      </c>
-      <c r="M75" t="n">
-        <v/>
-      </c>
-      <c r="N75" t="n">
-        <v/>
-      </c>
-      <c r="O75" t="n">
-        <v/>
-      </c>
-      <c r="P75" t="n">
-        <v/>
-      </c>
       <c r="Q75" t="inlineStr">
         <is>
           <t>D0=403.13; 最新=2026-06-04; 相对D0=3.58%</t>
@@ -5708,24 +4586,6 @@
       <c r="J76" t="n">
         <v>962.25</v>
       </c>
-      <c r="K76" t="n">
-        <v/>
-      </c>
-      <c r="L76" t="n">
-        <v/>
-      </c>
-      <c r="M76" t="n">
-        <v/>
-      </c>
-      <c r="N76" t="n">
-        <v/>
-      </c>
-      <c r="O76" t="n">
-        <v/>
-      </c>
-      <c r="P76" t="n">
-        <v/>
-      </c>
       <c r="Q76" t="inlineStr">
         <is>
           <t>D0=1070.47; 最新=2026-06-04; 相对D0=-10.11%</t>
@@ -5777,24 +4637,12 @@
       <c r="J77" s="5" t="n">
         <v>185</v>
       </c>
-      <c r="K77" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L77" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M77" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N77" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O77" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P77" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K77" s="5" t="n"/>
+      <c r="L77" s="5" t="n"/>
+      <c r="M77" s="5" t="n"/>
+      <c r="N77" s="5" t="n"/>
+      <c r="O77" s="5" t="n"/>
+      <c r="P77" s="5" t="n"/>
       <c r="Q77" s="5" t="inlineStr">
         <is>
           <t>D0=183.36; 最新=2026-06-04; 相对D0=0.89%</t>
@@ -5846,24 +4694,12 @@
       <c r="J78" s="5" t="n">
         <v>69.155</v>
       </c>
-      <c r="K78" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L78" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M78" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N78" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O78" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P78" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K78" s="5" t="n"/>
+      <c r="L78" s="5" t="n"/>
+      <c r="M78" s="5" t="n"/>
+      <c r="N78" s="5" t="n"/>
+      <c r="O78" s="5" t="n"/>
+      <c r="P78" s="5" t="n"/>
       <c r="Q78" s="5" t="inlineStr">
         <is>
           <t>D0=69.63; 最新=2026-06-04; 相对D0=-0.68%</t>
@@ -5915,24 +4751,12 @@
       <c r="J79" s="5" t="n">
         <v>629.355</v>
       </c>
-      <c r="K79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O79" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P79" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K79" s="5" t="n"/>
+      <c r="L79" s="5" t="n"/>
+      <c r="M79" s="5" t="n"/>
+      <c r="N79" s="5" t="n"/>
+      <c r="O79" s="5" t="n"/>
+      <c r="P79" s="5" t="n"/>
       <c r="Q79" s="5" t="inlineStr">
         <is>
           <t>D0=612.34; 最新=2026-06-04; 相对D0=2.78%</t>
@@ -5984,24 +4808,6 @@
       <c r="J80" t="n">
         <v>22.66</v>
       </c>
-      <c r="K80" t="n">
-        <v/>
-      </c>
-      <c r="L80" t="n">
-        <v/>
-      </c>
-      <c r="M80" t="n">
-        <v/>
-      </c>
-      <c r="N80" t="n">
-        <v/>
-      </c>
-      <c r="O80" t="n">
-        <v/>
-      </c>
-      <c r="P80" t="n">
-        <v/>
-      </c>
       <c r="Q80" t="inlineStr">
         <is>
           <t>D0=22.62; 最新=2026-06-04; 相对D0=0.18%</t>
@@ -6053,24 +4859,12 @@
       <c r="J81" s="5" t="n">
         <v>131.7</v>
       </c>
-      <c r="K81" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L81" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M81" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N81" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O81" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P81" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K81" s="5" t="n"/>
+      <c r="L81" s="5" t="n"/>
+      <c r="M81" s="5" t="n"/>
+      <c r="N81" s="5" t="n"/>
+      <c r="O81" s="5" t="n"/>
+      <c r="P81" s="5" t="n"/>
       <c r="Q81" s="5" t="inlineStr">
         <is>
           <t>D0=134.61; 最新=2026-06-04; 相对D0=-2.16%; 历史重复2次; 重复日期=2026-05-28, 2026-06-02</t>
@@ -6122,24 +4916,12 @@
       <c r="J82" s="5" t="n">
         <v>65.61</v>
       </c>
-      <c r="K82" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L82" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M82" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N82" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O82" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P82" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K82" s="5" t="n"/>
+      <c r="L82" s="5" t="n"/>
+      <c r="M82" s="5" t="n"/>
+      <c r="N82" s="5" t="n"/>
+      <c r="O82" s="5" t="n"/>
+      <c r="P82" s="5" t="n"/>
       <c r="Q82" s="5" t="inlineStr">
         <is>
           <t>D0=68.70; 最新=2026-06-04; 相对D0=-4.50%; 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -6191,24 +4973,12 @@
       <c r="J83" s="5" t="n">
         <v>276.586</v>
       </c>
-      <c r="K83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O83" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P83" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K83" s="5" t="n"/>
+      <c r="L83" s="5" t="n"/>
+      <c r="M83" s="5" t="n"/>
+      <c r="N83" s="5" t="n"/>
+      <c r="O83" s="5" t="n"/>
+      <c r="P83" s="5" t="n"/>
       <c r="Q83" s="5" t="inlineStr">
         <is>
           <t>D0=274.17; 最新=2026-06-04; 相对D0=0.88%</t>
@@ -6260,24 +5030,6 @@
       <c r="J84" t="n">
         <v>57.47</v>
       </c>
-      <c r="K84" t="n">
-        <v/>
-      </c>
-      <c r="L84" t="n">
-        <v/>
-      </c>
-      <c r="M84" t="n">
-        <v/>
-      </c>
-      <c r="N84" t="n">
-        <v/>
-      </c>
-      <c r="O84" t="n">
-        <v/>
-      </c>
-      <c r="P84" t="n">
-        <v/>
-      </c>
       <c r="Q84" t="inlineStr">
         <is>
           <t>D0=56.31; 最新=2026-06-04; 相对D0=2.06%</t>
@@ -6329,24 +5081,6 @@
       <c r="J85" t="n">
         <v>105.1</v>
       </c>
-      <c r="K85" t="n">
-        <v/>
-      </c>
-      <c r="L85" t="n">
-        <v/>
-      </c>
-      <c r="M85" t="n">
-        <v/>
-      </c>
-      <c r="N85" t="n">
-        <v/>
-      </c>
-      <c r="O85" t="n">
-        <v/>
-      </c>
-      <c r="P85" t="n">
-        <v/>
-      </c>
       <c r="Q85" t="inlineStr">
         <is>
           <t>D0=106.94; 最新=2026-06-04; 相对D0=-1.72%</t>
@@ -6398,24 +5132,12 @@
       <c r="J86" s="5" t="n">
         <v>12.0901</v>
       </c>
-      <c r="K86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O86" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P86" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K86" s="5" t="n"/>
+      <c r="L86" s="5" t="n"/>
+      <c r="M86" s="5" t="n"/>
+      <c r="N86" s="5" t="n"/>
+      <c r="O86" s="5" t="n"/>
+      <c r="P86" s="5" t="n"/>
       <c r="Q86" s="5" t="inlineStr">
         <is>
           <t>D0=12.22; 最新=2026-06-04; 相对D0=-1.06%</t>
@@ -6467,24 +5189,6 @@
       <c r="J87" t="n">
         <v>84.91500000000001</v>
       </c>
-      <c r="K87" t="n">
-        <v/>
-      </c>
-      <c r="L87" t="n">
-        <v/>
-      </c>
-      <c r="M87" t="n">
-        <v/>
-      </c>
-      <c r="N87" t="n">
-        <v/>
-      </c>
-      <c r="O87" t="n">
-        <v/>
-      </c>
-      <c r="P87" t="n">
-        <v/>
-      </c>
       <c r="Q87" t="inlineStr">
         <is>
           <t>D0=84.64; 最新=2026-06-04; 相对D0=0.32%</t>
@@ -6536,24 +5240,12 @@
       <c r="J88" s="5" t="n">
         <v>14.315</v>
       </c>
-      <c r="K88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P88" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K88" s="5" t="n"/>
+      <c r="L88" s="5" t="n"/>
+      <c r="M88" s="5" t="n"/>
+      <c r="N88" s="5" t="n"/>
+      <c r="O88" s="5" t="n"/>
+      <c r="P88" s="5" t="n"/>
       <c r="Q88" s="5" t="inlineStr">
         <is>
           <t>D0=13.51; 最新=2026-06-04; 相对D0=5.96%</t>
@@ -6605,24 +5297,12 @@
       <c r="J89" s="5" t="n">
         <v>17.58</v>
       </c>
-      <c r="K89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P89" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K89" s="5" t="n"/>
+      <c r="L89" s="5" t="n"/>
+      <c r="M89" s="5" t="n"/>
+      <c r="N89" s="5" t="n"/>
+      <c r="O89" s="5" t="n"/>
+      <c r="P89" s="5" t="n"/>
       <c r="Q89" s="5" t="inlineStr">
         <is>
           <t>D0=18.40; 最新=2026-06-04; 相对D0=-4.46%; 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -6674,24 +5354,6 @@
       <c r="J90" t="n">
         <v>320.39</v>
       </c>
-      <c r="K90" t="n">
-        <v/>
-      </c>
-      <c r="L90" t="n">
-        <v/>
-      </c>
-      <c r="M90" t="n">
-        <v/>
-      </c>
-      <c r="N90" t="n">
-        <v/>
-      </c>
-      <c r="O90" t="n">
-        <v/>
-      </c>
-      <c r="P90" t="n">
-        <v/>
-      </c>
       <c r="Q90" t="inlineStr">
         <is>
           <t>D0=323.91; 最新=2026-06-04; 相对D0=-1.09%; 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -6743,24 +5405,6 @@
       <c r="J91" t="n">
         <v>51.635</v>
       </c>
-      <c r="K91" t="n">
-        <v/>
-      </c>
-      <c r="L91" t="n">
-        <v/>
-      </c>
-      <c r="M91" t="n">
-        <v/>
-      </c>
-      <c r="N91" t="n">
-        <v/>
-      </c>
-      <c r="O91" t="n">
-        <v/>
-      </c>
-      <c r="P91" t="n">
-        <v/>
-      </c>
       <c r="Q91" t="inlineStr">
         <is>
           <t>D0=50.99; 最新=2026-06-04; 相对D0=1.26%</t>
@@ -6812,24 +5456,6 @@
       <c r="J92" t="n">
         <v>198.7336</v>
       </c>
-      <c r="K92" t="n">
-        <v/>
-      </c>
-      <c r="L92" t="n">
-        <v/>
-      </c>
-      <c r="M92" t="n">
-        <v/>
-      </c>
-      <c r="N92" t="n">
-        <v/>
-      </c>
-      <c r="O92" t="n">
-        <v/>
-      </c>
-      <c r="P92" t="n">
-        <v/>
-      </c>
       <c r="Q92" t="inlineStr">
         <is>
           <t>D0=179.83; 最新=2026-06-04; 相对D0=10.51%</t>
@@ -6881,24 +5507,12 @@
       <c r="J93" s="5" t="n">
         <v>253.87</v>
       </c>
-      <c r="K93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O93" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P93" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K93" s="5" t="n"/>
+      <c r="L93" s="5" t="n"/>
+      <c r="M93" s="5" t="n"/>
+      <c r="N93" s="5" t="n"/>
+      <c r="O93" s="5" t="n"/>
+      <c r="P93" s="5" t="n"/>
       <c r="Q93" s="5" t="inlineStr">
         <is>
           <t>D0=271.85; 最新=2026-06-04; 相对D0=-6.61%</t>
@@ -6919,7 +5533,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -6945,24 +5558,6 @@
       </c>
       <c r="J94" t="n">
         <v>91.47</v>
-      </c>
-      <c r="K94" t="n">
-        <v/>
-      </c>
-      <c r="L94" t="n">
-        <v/>
-      </c>
-      <c r="M94" t="n">
-        <v/>
-      </c>
-      <c r="N94" t="n">
-        <v/>
-      </c>
-      <c r="O94" t="n">
-        <v/>
-      </c>
-      <c r="P94" t="n">
-        <v/>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
@@ -7015,24 +5610,6 @@
       <c r="J95" t="n">
         <v>16.715</v>
       </c>
-      <c r="K95" t="n">
-        <v/>
-      </c>
-      <c r="L95" t="n">
-        <v/>
-      </c>
-      <c r="M95" t="n">
-        <v/>
-      </c>
-      <c r="N95" t="n">
-        <v/>
-      </c>
-      <c r="O95" t="n">
-        <v/>
-      </c>
-      <c r="P95" t="n">
-        <v/>
-      </c>
       <c r="Q95" t="inlineStr">
         <is>
           <t>D0=16.46; 最新=2026-06-04; 相对D0=1.55%</t>
@@ -7084,24 +5661,6 @@
       <c r="J96" t="n">
         <v>28.36</v>
       </c>
-      <c r="K96" t="n">
-        <v/>
-      </c>
-      <c r="L96" t="n">
-        <v/>
-      </c>
-      <c r="M96" t="n">
-        <v/>
-      </c>
-      <c r="N96" t="n">
-        <v/>
-      </c>
-      <c r="O96" t="n">
-        <v/>
-      </c>
-      <c r="P96" t="n">
-        <v/>
-      </c>
       <c r="Q96" t="inlineStr">
         <is>
           <t>D0=25.20; 最新=2026-06-04; 相对D0=12.54%</t>
@@ -7153,24 +5712,6 @@
       <c r="J97" t="n">
         <v>51.52</v>
       </c>
-      <c r="K97" t="n">
-        <v/>
-      </c>
-      <c r="L97" t="n">
-        <v/>
-      </c>
-      <c r="M97" t="n">
-        <v/>
-      </c>
-      <c r="N97" t="n">
-        <v/>
-      </c>
-      <c r="O97" t="n">
-        <v/>
-      </c>
-      <c r="P97" t="n">
-        <v/>
-      </c>
       <c r="Q97" t="inlineStr">
         <is>
           <t>D0=50.44; 最新=2026-06-04; 相对D0=2.14%</t>
@@ -7222,24 +5763,12 @@
       <c r="J98" s="5" t="n">
         <v>276.586</v>
       </c>
-      <c r="K98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O98" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P98" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K98" s="5" t="n"/>
+      <c r="L98" s="5" t="n"/>
+      <c r="M98" s="5" t="n"/>
+      <c r="N98" s="5" t="n"/>
+      <c r="O98" s="5" t="n"/>
+      <c r="P98" s="5" t="n"/>
       <c r="Q98" s="5" t="inlineStr">
         <is>
           <t>D0=266.89; 最新=2026-06-04; 相对D0=3.63%</t>
@@ -7291,24 +5820,6 @@
       <c r="J99" t="n">
         <v>234.01</v>
       </c>
-      <c r="K99" t="n">
-        <v/>
-      </c>
-      <c r="L99" t="n">
-        <v/>
-      </c>
-      <c r="M99" t="n">
-        <v/>
-      </c>
-      <c r="N99" t="n">
-        <v/>
-      </c>
-      <c r="O99" t="n">
-        <v/>
-      </c>
-      <c r="P99" t="n">
-        <v/>
-      </c>
       <c r="Q99" t="inlineStr">
         <is>
           <t>D0=190.96; 最新=2026-06-04; 相对D0=22.54%</t>
@@ -7360,24 +5871,12 @@
       <c r="J100" s="5" t="n">
         <v>101.165</v>
       </c>
-      <c r="K100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O100" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P100" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K100" s="5" t="n"/>
+      <c r="L100" s="5" t="n"/>
+      <c r="M100" s="5" t="n"/>
+      <c r="N100" s="5" t="n"/>
+      <c r="O100" s="5" t="n"/>
+      <c r="P100" s="5" t="n"/>
       <c r="Q100" s="5" t="inlineStr">
         <is>
           <t>D0=89.07; 最新=2026-06-04; 相对D0=13.58%</t>
@@ -7429,24 +5928,6 @@
       <c r="J101" t="n">
         <v>397.02</v>
       </c>
-      <c r="K101" t="n">
-        <v/>
-      </c>
-      <c r="L101" t="n">
-        <v/>
-      </c>
-      <c r="M101" t="n">
-        <v/>
-      </c>
-      <c r="N101" t="n">
-        <v/>
-      </c>
-      <c r="O101" t="n">
-        <v/>
-      </c>
-      <c r="P101" t="n">
-        <v/>
-      </c>
       <c r="Q101" t="inlineStr">
         <is>
           <t>D0=384.01; 最新=2026-06-04; 相对D0=3.39%</t>
@@ -7467,7 +5948,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -7493,24 +5973,6 @@
       </c>
       <c r="J102" t="n">
         <v>91.47</v>
-      </c>
-      <c r="K102" t="n">
-        <v/>
-      </c>
-      <c r="L102" t="n">
-        <v/>
-      </c>
-      <c r="M102" t="n">
-        <v/>
-      </c>
-      <c r="N102" t="n">
-        <v/>
-      </c>
-      <c r="O102" t="n">
-        <v/>
-      </c>
-      <c r="P102" t="n">
-        <v/>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
@@ -7563,24 +6025,12 @@
       <c r="J103" s="5" t="n">
         <v>114.45</v>
       </c>
-      <c r="K103" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L103" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M103" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N103" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O103" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P103" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K103" s="5" t="n"/>
+      <c r="L103" s="5" t="n"/>
+      <c r="M103" s="5" t="n"/>
+      <c r="N103" s="5" t="n"/>
+      <c r="O103" s="5" t="n"/>
+      <c r="P103" s="5" t="n"/>
       <c r="Q103" s="5" t="inlineStr">
         <is>
           <t>D0=110.63; 最新=2026-06-04; 相对D0=3.45%</t>
@@ -7632,24 +6082,6 @@
       <c r="J104" t="n">
         <v>90.11499999999999</v>
       </c>
-      <c r="K104" t="n">
-        <v/>
-      </c>
-      <c r="L104" t="n">
-        <v/>
-      </c>
-      <c r="M104" t="n">
-        <v/>
-      </c>
-      <c r="N104" t="n">
-        <v/>
-      </c>
-      <c r="O104" t="n">
-        <v/>
-      </c>
-      <c r="P104" t="n">
-        <v/>
-      </c>
       <c r="Q104" t="inlineStr">
         <is>
           <t>D0=83.68; 最新=2026-06-04; 相对D0=7.69%</t>
@@ -7701,24 +6133,12 @@
       <c r="J105" s="5" t="n">
         <v>189.055</v>
       </c>
-      <c r="K105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P105" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K105" s="5" t="n"/>
+      <c r="L105" s="5" t="n"/>
+      <c r="M105" s="5" t="n"/>
+      <c r="N105" s="5" t="n"/>
+      <c r="O105" s="5" t="n"/>
+      <c r="P105" s="5" t="n"/>
       <c r="Q105" s="5" t="inlineStr">
         <is>
           <t>D0=176.17; 最新=2026-06-04; 相对D0=7.31%</t>
@@ -7770,24 +6190,6 @@
       <c r="J106" t="n">
         <v>707.8624</v>
       </c>
-      <c r="K106" t="n">
-        <v/>
-      </c>
-      <c r="L106" t="n">
-        <v/>
-      </c>
-      <c r="M106" t="n">
-        <v/>
-      </c>
-      <c r="N106" t="n">
-        <v/>
-      </c>
-      <c r="O106" t="n">
-        <v/>
-      </c>
-      <c r="P106" t="n">
-        <v/>
-      </c>
       <c r="Q106" t="inlineStr">
         <is>
           <t>D0=671.00; 最新=2026-06-04; 相对D0=5.49%</t>
@@ -7839,24 +6241,6 @@
       <c r="J107" t="n">
         <v>108.39</v>
       </c>
-      <c r="K107" t="n">
-        <v/>
-      </c>
-      <c r="L107" t="n">
-        <v/>
-      </c>
-      <c r="M107" t="n">
-        <v/>
-      </c>
-      <c r="N107" t="n">
-        <v/>
-      </c>
-      <c r="O107" t="n">
-        <v/>
-      </c>
-      <c r="P107" t="n">
-        <v/>
-      </c>
       <c r="Q107" t="inlineStr">
         <is>
           <t>D0=106.86; 最新=2026-06-04; 相对D0=1.43%</t>
@@ -7877,7 +6261,6 @@
           <t>EQIX</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -7903,24 +6286,6 @@
       </c>
       <c r="J108" t="n">
         <v>1081.6125</v>
-      </c>
-      <c r="K108" t="n">
-        <v/>
-      </c>
-      <c r="L108" t="n">
-        <v/>
-      </c>
-      <c r="M108" t="n">
-        <v/>
-      </c>
-      <c r="N108" t="n">
-        <v/>
-      </c>
-      <c r="O108" t="n">
-        <v/>
-      </c>
-      <c r="P108" t="n">
-        <v/>
       </c>
       <c r="Q108" t="inlineStr">
         <is>
@@ -7973,24 +6338,6 @@
       <c r="J109" t="n">
         <v>148.56</v>
       </c>
-      <c r="K109" t="n">
-        <v/>
-      </c>
-      <c r="L109" t="n">
-        <v/>
-      </c>
-      <c r="M109" t="n">
-        <v/>
-      </c>
-      <c r="N109" t="n">
-        <v/>
-      </c>
-      <c r="O109" t="n">
-        <v/>
-      </c>
-      <c r="P109" t="n">
-        <v/>
-      </c>
       <c r="Q109" t="inlineStr">
         <is>
           <t>D0=129.70; 最新=2026-06-04; 相对D0=14.54%</t>
@@ -8042,24 +6389,12 @@
       <c r="J110" s="5" t="n">
         <v>372.22</v>
       </c>
-      <c r="K110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P110" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K110" s="5" t="n"/>
+      <c r="L110" s="5" t="n"/>
+      <c r="M110" s="5" t="n"/>
+      <c r="N110" s="5" t="n"/>
+      <c r="O110" s="5" t="n"/>
+      <c r="P110" s="5" t="n"/>
       <c r="Q110" s="5" t="inlineStr">
         <is>
           <t>D0=390.13; 最新=2026-06-04; 相对D0=-4.59%</t>
@@ -8111,24 +6446,6 @@
       <c r="J111" t="n">
         <v>86.62</v>
       </c>
-      <c r="K111" t="n">
-        <v/>
-      </c>
-      <c r="L111" t="n">
-        <v/>
-      </c>
-      <c r="M111" t="n">
-        <v/>
-      </c>
-      <c r="N111" t="n">
-        <v/>
-      </c>
-      <c r="O111" t="n">
-        <v/>
-      </c>
-      <c r="P111" t="n">
-        <v/>
-      </c>
       <c r="Q111" t="inlineStr">
         <is>
           <t>D0=84.84; 最新=2026-06-04; 相对D0=2.10%</t>
@@ -8180,24 +6497,12 @@
       <c r="J112" s="5" t="n">
         <v>99.70999999999999</v>
       </c>
-      <c r="K112" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L112" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M112" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N112" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O112" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P112" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K112" s="5" t="n"/>
+      <c r="L112" s="5" t="n"/>
+      <c r="M112" s="5" t="n"/>
+      <c r="N112" s="5" t="n"/>
+      <c r="O112" s="5" t="n"/>
+      <c r="P112" s="5" t="n"/>
       <c r="Q112" s="5" t="inlineStr">
         <is>
           <t>D0=95.68; 最新=2026-06-04; 相对D0=4.21%</t>
@@ -8249,24 +6554,12 @@
       <c r="J113" s="5" t="n">
         <v>185</v>
       </c>
-      <c r="K113" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L113" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M113" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N113" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O113" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P113" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K113" s="5" t="n"/>
+      <c r="L113" s="5" t="n"/>
+      <c r="M113" s="5" t="n"/>
+      <c r="N113" s="5" t="n"/>
+      <c r="O113" s="5" t="n"/>
+      <c r="P113" s="5" t="n"/>
       <c r="Q113" s="5" t="inlineStr">
         <is>
           <t>D0=185.46; 最新=2026-06-04; 相对D0=-0.25%</t>
@@ -8318,24 +6611,12 @@
       <c r="J114" s="5" t="n">
         <v>379.68</v>
       </c>
-      <c r="K114" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L114" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M114" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N114" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O114" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P114" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K114" s="5" t="n"/>
+      <c r="L114" s="5" t="n"/>
+      <c r="M114" s="5" t="n"/>
+      <c r="N114" s="5" t="n"/>
+      <c r="O114" s="5" t="n"/>
+      <c r="P114" s="5" t="n"/>
       <c r="Q114" s="5" t="inlineStr">
         <is>
           <t>D0=325.68; 最新=2026-06-04; 相对D0=16.58%</t>
@@ -8387,24 +6668,12 @@
       <c r="J115" s="5" t="n">
         <v>426.7013</v>
       </c>
-      <c r="K115" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L115" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M115" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N115" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O115" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P115" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K115" s="5" t="n"/>
+      <c r="L115" s="5" t="n"/>
+      <c r="M115" s="5" t="n"/>
+      <c r="N115" s="5" t="n"/>
+      <c r="O115" s="5" t="n"/>
+      <c r="P115" s="5" t="n"/>
       <c r="Q115" s="5" t="inlineStr">
         <is>
           <t>D0=426.99; 最新=2026-06-04; 相对D0=-0.07%</t>
@@ -8456,24 +6725,6 @@
       <c r="J116" t="n">
         <v>255.1999</v>
       </c>
-      <c r="K116" t="n">
-        <v/>
-      </c>
-      <c r="L116" t="n">
-        <v/>
-      </c>
-      <c r="M116" t="n">
-        <v/>
-      </c>
-      <c r="N116" t="n">
-        <v/>
-      </c>
-      <c r="O116" t="n">
-        <v/>
-      </c>
-      <c r="P116" t="n">
-        <v/>
-      </c>
       <c r="Q116" t="inlineStr">
         <is>
           <t>D0=226.34; 最新=2026-06-04; 相对D0=12.75%</t>
@@ -8525,24 +6776,12 @@
       <c r="J117" s="5" t="n">
         <v>131.7</v>
       </c>
-      <c r="K117" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L117" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M117" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N117" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O117" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P117" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K117" s="5" t="n"/>
+      <c r="L117" s="5" t="n"/>
+      <c r="M117" s="5" t="n"/>
+      <c r="N117" s="5" t="n"/>
+      <c r="O117" s="5" t="n"/>
+      <c r="P117" s="5" t="n"/>
       <c r="Q117" s="5" t="inlineStr">
         <is>
           <t>D0=133.31; 最新=2026-06-04; 相对D0=-1.21%</t>
@@ -8594,24 +6833,6 @@
       <c r="J118" t="n">
         <v>123.21</v>
       </c>
-      <c r="K118" t="n">
-        <v/>
-      </c>
-      <c r="L118" t="n">
-        <v/>
-      </c>
-      <c r="M118" t="n">
-        <v/>
-      </c>
-      <c r="N118" t="n">
-        <v/>
-      </c>
-      <c r="O118" t="n">
-        <v/>
-      </c>
-      <c r="P118" t="n">
-        <v/>
-      </c>
       <c r="Q118" t="inlineStr">
         <is>
           <t>D0=94.72; 最新=2026-06-04; 相对D0=30.08%</t>
@@ -8663,24 +6884,6 @@
       <c r="J119" t="n">
         <v>271.48</v>
       </c>
-      <c r="K119" t="n">
-        <v/>
-      </c>
-      <c r="L119" t="n">
-        <v/>
-      </c>
-      <c r="M119" t="n">
-        <v/>
-      </c>
-      <c r="N119" t="n">
-        <v/>
-      </c>
-      <c r="O119" t="n">
-        <v/>
-      </c>
-      <c r="P119" t="n">
-        <v/>
-      </c>
       <c r="Q119" t="inlineStr">
         <is>
           <t>D0=257.77; 最新=2026-06-04; 相对D0=5.32%</t>
@@ -8732,24 +6935,12 @@
       <c r="J120" s="5" t="n">
         <v>140.68</v>
       </c>
-      <c r="K120" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L120" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M120" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N120" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O120" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P120" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K120" s="5" t="n"/>
+      <c r="L120" s="5" t="n"/>
+      <c r="M120" s="5" t="n"/>
+      <c r="N120" s="5" t="n"/>
+      <c r="O120" s="5" t="n"/>
+      <c r="P120" s="5" t="n"/>
       <c r="Q120" s="5" t="inlineStr">
         <is>
           <t>D0=143.34; 最新=2026-06-04; 相对D0=-1.86%</t>
@@ -8801,24 +6992,12 @@
       <c r="J121" s="5" t="n">
         <v>181.05</v>
       </c>
-      <c r="K121" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L121" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M121" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N121" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O121" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P121" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K121" s="5" t="n"/>
+      <c r="L121" s="5" t="n"/>
+      <c r="M121" s="5" t="n"/>
+      <c r="N121" s="5" t="n"/>
+      <c r="O121" s="5" t="n"/>
+      <c r="P121" s="5" t="n"/>
       <c r="Q121" s="5" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-04; 相对D0=5.47%</t>
@@ -8870,24 +7049,12 @@
       <c r="J122" s="5" t="n">
         <v>264.2</v>
       </c>
-      <c r="K122" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L122" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M122" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N122" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O122" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P122" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K122" s="5" t="n"/>
+      <c r="L122" s="5" t="n"/>
+      <c r="M122" s="5" t="n"/>
+      <c r="N122" s="5" t="n"/>
+      <c r="O122" s="5" t="n"/>
+      <c r="P122" s="5" t="n"/>
       <c r="Q122" s="5" t="inlineStr">
         <is>
           <t>D0=287.75; 最新=2026-06-04; 相对D0=-8.18%</t>
@@ -8939,24 +7106,6 @@
       <c r="J123" t="n">
         <v>163.16</v>
       </c>
-      <c r="K123" t="n">
-        <v/>
-      </c>
-      <c r="L123" t="n">
-        <v/>
-      </c>
-      <c r="M123" t="n">
-        <v/>
-      </c>
-      <c r="N123" t="n">
-        <v/>
-      </c>
-      <c r="O123" t="n">
-        <v/>
-      </c>
-      <c r="P123" t="n">
-        <v/>
-      </c>
       <c r="Q123" t="inlineStr">
         <is>
           <t>D0=189.03; 最新=2026-06-04; 相对D0=-13.69%</t>
@@ -9008,24 +7157,12 @@
       <c r="J124" s="5" t="n">
         <v>189.055</v>
       </c>
-      <c r="K124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P124" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K124" s="5" t="n"/>
+      <c r="L124" s="5" t="n"/>
+      <c r="M124" s="5" t="n"/>
+      <c r="N124" s="5" t="n"/>
+      <c r="O124" s="5" t="n"/>
+      <c r="P124" s="5" t="n"/>
       <c r="Q124" s="5" t="inlineStr">
         <is>
           <t>D0=191.10; 最新=2026-06-04; 相对D0=-1.07%</t>
@@ -9077,24 +7214,6 @@
       <c r="J125" t="n">
         <v>108.39</v>
       </c>
-      <c r="K125" t="n">
-        <v/>
-      </c>
-      <c r="L125" t="n">
-        <v/>
-      </c>
-      <c r="M125" t="n">
-        <v/>
-      </c>
-      <c r="N125" t="n">
-        <v/>
-      </c>
-      <c r="O125" t="n">
-        <v/>
-      </c>
-      <c r="P125" t="n">
-        <v/>
-      </c>
       <c r="Q125" t="inlineStr">
         <is>
           <t>D0=109.53; 最新=2026-06-04; 相对D0=-1.04%</t>
@@ -9146,24 +7265,12 @@
       <c r="J126" s="5" t="n">
         <v>47.42</v>
       </c>
-      <c r="K126" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L126" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M126" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N126" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O126" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P126" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K126" s="5" t="n"/>
+      <c r="L126" s="5" t="n"/>
+      <c r="M126" s="5" t="n"/>
+      <c r="N126" s="5" t="n"/>
+      <c r="O126" s="5" t="n"/>
+      <c r="P126" s="5" t="n"/>
       <c r="Q126" s="5" t="inlineStr">
         <is>
           <t>D0=48.42; 最新=2026-06-04; 相对D0=-2.07%</t>
@@ -9215,24 +7322,6 @@
       <c r="J127" t="n">
         <v>2118.385</v>
       </c>
-      <c r="K127" t="n">
-        <v/>
-      </c>
-      <c r="L127" t="n">
-        <v/>
-      </c>
-      <c r="M127" t="n">
-        <v/>
-      </c>
-      <c r="N127" t="n">
-        <v/>
-      </c>
-      <c r="O127" t="n">
-        <v/>
-      </c>
-      <c r="P127" t="n">
-        <v/>
-      </c>
       <c r="Q127" t="inlineStr">
         <is>
           <t>D0=1921.71; 最新=2026-06-04; 相对D0=10.23%</t>
@@ -9284,24 +7373,12 @@
       <c r="J128" s="5" t="n">
         <v>379.68</v>
       </c>
-      <c r="K128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P128" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K128" s="5" t="n"/>
+      <c r="L128" s="5" t="n"/>
+      <c r="M128" s="5" t="n"/>
+      <c r="N128" s="5" t="n"/>
+      <c r="O128" s="5" t="n"/>
+      <c r="P128" s="5" t="n"/>
       <c r="Q128" s="5" t="inlineStr">
         <is>
           <t>D0=335.55; 最新=2026-06-04; 相对D0=13.15%</t>
@@ -9353,24 +7430,12 @@
       <c r="J129" s="5" t="n">
         <v>408.5515</v>
       </c>
-      <c r="K129" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L129" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M129" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N129" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O129" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P129" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K129" s="5" t="n"/>
+      <c r="L129" s="5" t="n"/>
+      <c r="M129" s="5" t="n"/>
+      <c r="N129" s="5" t="n"/>
+      <c r="O129" s="5" t="n"/>
+      <c r="P129" s="5" t="n"/>
       <c r="Q129" s="5" t="inlineStr">
         <is>
           <t>D0=374.31; 最新=2026-06-04; 相对D0=9.15%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -9422,24 +7487,12 @@
       <c r="J130" s="5" t="n">
         <v>14.315</v>
       </c>
-      <c r="K130" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L130" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M130" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N130" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O130" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P130" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K130" s="5" t="n"/>
+      <c r="L130" s="5" t="n"/>
+      <c r="M130" s="5" t="n"/>
+      <c r="N130" s="5" t="n"/>
+      <c r="O130" s="5" t="n"/>
+      <c r="P130" s="5" t="n"/>
       <c r="Q130" s="5" t="inlineStr">
         <is>
           <t>D0=13.77; 最新=2026-06-04; 相对D0=3.96%</t>
@@ -9491,24 +7544,6 @@
       <c r="J131" t="n">
         <v>198.7336</v>
       </c>
-      <c r="K131" t="n">
-        <v/>
-      </c>
-      <c r="L131" t="n">
-        <v/>
-      </c>
-      <c r="M131" t="n">
-        <v/>
-      </c>
-      <c r="N131" t="n">
-        <v/>
-      </c>
-      <c r="O131" t="n">
-        <v/>
-      </c>
-      <c r="P131" t="n">
-        <v/>
-      </c>
       <c r="Q131" t="inlineStr">
         <is>
           <t>D0=185.67; 最新=2026-06-04; 相对D0=7.04%</t>
@@ -9560,24 +7595,6 @@
       <c r="J132" t="n">
         <v>14.73</v>
       </c>
-      <c r="K132" t="n">
-        <v/>
-      </c>
-      <c r="L132" t="n">
-        <v/>
-      </c>
-      <c r="M132" t="n">
-        <v/>
-      </c>
-      <c r="N132" t="n">
-        <v/>
-      </c>
-      <c r="O132" t="n">
-        <v/>
-      </c>
-      <c r="P132" t="n">
-        <v/>
-      </c>
       <c r="Q132" t="inlineStr">
         <is>
           <t>D0=14.70; 最新=2026-06-04; 相对D0=0.20%</t>
@@ -9629,24 +7646,12 @@
       <c r="J133" s="5" t="n">
         <v>75.23999999999999</v>
       </c>
-      <c r="K133" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L133" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M133" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N133" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O133" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P133" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K133" s="5" t="n"/>
+      <c r="L133" s="5" t="n"/>
+      <c r="M133" s="5" t="n"/>
+      <c r="N133" s="5" t="n"/>
+      <c r="O133" s="5" t="n"/>
+      <c r="P133" s="5" t="n"/>
       <c r="Q133" s="5" t="inlineStr">
         <is>
           <t>D0=72.75; 最新=2026-06-04; 相对D0=3.42%</t>
@@ -9698,24 +7703,12 @@
       <c r="J134" s="5" t="n">
         <v>119.06</v>
       </c>
-      <c r="K134" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L134" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M134" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N134" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O134" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P134" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K134" s="5" t="n"/>
+      <c r="L134" s="5" t="n"/>
+      <c r="M134" s="5" t="n"/>
+      <c r="N134" s="5" t="n"/>
+      <c r="O134" s="5" t="n"/>
+      <c r="P134" s="5" t="n"/>
       <c r="Q134" s="5" t="inlineStr">
         <is>
           <t>D0=115.58; 最新=2026-06-04; 相对D0=3.01%; 历史重复2次; 重复日期=2026-06-02, 2026-06-03</t>
@@ -9767,24 +7760,12 @@
       <c r="J135" s="5" t="n">
         <v>189.65</v>
       </c>
-      <c r="K135" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L135" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M135" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N135" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O135" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P135" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K135" s="5" t="n"/>
+      <c r="L135" s="5" t="n"/>
+      <c r="M135" s="5" t="n"/>
+      <c r="N135" s="5" t="n"/>
+      <c r="O135" s="5" t="n"/>
+      <c r="P135" s="5" t="n"/>
       <c r="Q135" s="5" t="inlineStr">
         <is>
           <t>D0=185.83; 最新=2026-06-04; 相对D0=2.06%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -9836,24 +7817,12 @@
       <c r="J136" s="5" t="n">
         <v>140.775</v>
       </c>
-      <c r="K136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P136" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K136" s="5" t="n"/>
+      <c r="L136" s="5" t="n"/>
+      <c r="M136" s="5" t="n"/>
+      <c r="N136" s="5" t="n"/>
+      <c r="O136" s="5" t="n"/>
+      <c r="P136" s="5" t="n"/>
       <c r="Q136" s="5" t="inlineStr">
         <is>
           <t>D0=136.62; 最新=2026-06-04; 相对D0=3.04%</t>
@@ -9905,24 +7874,6 @@
       <c r="J137" t="n">
         <v>7.9547</v>
       </c>
-      <c r="K137" t="n">
-        <v/>
-      </c>
-      <c r="L137" t="n">
-        <v/>
-      </c>
-      <c r="M137" t="n">
-        <v/>
-      </c>
-      <c r="N137" t="n">
-        <v/>
-      </c>
-      <c r="O137" t="n">
-        <v/>
-      </c>
-      <c r="P137" t="n">
-        <v/>
-      </c>
       <c r="Q137" t="inlineStr">
         <is>
           <t>D0=8.97; 最新=2026-06-04; 相对D0=-11.32%</t>
@@ -9974,24 +7925,6 @@
       <c r="J138" t="n">
         <v>26.23</v>
       </c>
-      <c r="K138" t="n">
-        <v/>
-      </c>
-      <c r="L138" t="n">
-        <v/>
-      </c>
-      <c r="M138" t="n">
-        <v/>
-      </c>
-      <c r="N138" t="n">
-        <v/>
-      </c>
-      <c r="O138" t="n">
-        <v/>
-      </c>
-      <c r="P138" t="n">
-        <v/>
-      </c>
       <c r="Q138" t="inlineStr">
         <is>
           <t>D0=27.15; 最新=2026-06-04; 相对D0=-3.39%</t>
@@ -10043,24 +7976,6 @@
       <c r="J139" t="n">
         <v>51.52</v>
       </c>
-      <c r="K139" t="n">
-        <v/>
-      </c>
-      <c r="L139" t="n">
-        <v/>
-      </c>
-      <c r="M139" t="n">
-        <v/>
-      </c>
-      <c r="N139" t="n">
-        <v/>
-      </c>
-      <c r="O139" t="n">
-        <v/>
-      </c>
-      <c r="P139" t="n">
-        <v/>
-      </c>
       <c r="Q139" t="inlineStr">
         <is>
           <t>D0=50.55; 最新=2026-06-04; 相对D0=1.92%</t>
@@ -10112,24 +8027,12 @@
       <c r="J140" s="5" t="n">
         <v>185</v>
       </c>
-      <c r="K140" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L140" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M140" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N140" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O140" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P140" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K140" s="5" t="n"/>
+      <c r="L140" s="5" t="n"/>
+      <c r="M140" s="5" t="n"/>
+      <c r="N140" s="5" t="n"/>
+      <c r="O140" s="5" t="n"/>
+      <c r="P140" s="5" t="n"/>
       <c r="Q140" s="5" t="inlineStr">
         <is>
           <t>D0=189.00; 最新=2026-06-04; 相对D0=-2.12%</t>
@@ -10181,24 +8084,6 @@
       <c r="J141" t="n">
         <v>929.5</v>
       </c>
-      <c r="K141" t="n">
-        <v/>
-      </c>
-      <c r="L141" t="n">
-        <v/>
-      </c>
-      <c r="M141" t="n">
-        <v/>
-      </c>
-      <c r="N141" t="n">
-        <v/>
-      </c>
-      <c r="O141" t="n">
-        <v/>
-      </c>
-      <c r="P141" t="n">
-        <v/>
-      </c>
       <c r="Q141" t="inlineStr">
         <is>
           <t>D0=905.00; 最新=2026-06-04; 相对D0=2.71%</t>
@@ -10250,24 +8135,6 @@
       <c r="J142" t="n">
         <v>12.64</v>
       </c>
-      <c r="K142" t="n">
-        <v/>
-      </c>
-      <c r="L142" t="n">
-        <v/>
-      </c>
-      <c r="M142" t="n">
-        <v/>
-      </c>
-      <c r="N142" t="n">
-        <v/>
-      </c>
-      <c r="O142" t="n">
-        <v/>
-      </c>
-      <c r="P142" t="n">
-        <v/>
-      </c>
       <c r="Q142" t="inlineStr">
         <is>
           <t>D0=11.02; 最新=2026-06-04; 相对D0=14.70%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -10319,24 +8186,6 @@
       <c r="J143" t="n">
         <v>68.81999999999999</v>
       </c>
-      <c r="K143" t="n">
-        <v/>
-      </c>
-      <c r="L143" t="n">
-        <v/>
-      </c>
-      <c r="M143" t="n">
-        <v/>
-      </c>
-      <c r="N143" t="n">
-        <v/>
-      </c>
-      <c r="O143" t="n">
-        <v/>
-      </c>
-      <c r="P143" t="n">
-        <v/>
-      </c>
       <c r="Q143" t="inlineStr">
         <is>
           <t>D0=69.57; 最新=2026-06-04; 相对D0=-1.08%; 历史重复1次; 重复日期=2026-06-03</t>
@@ -10388,24 +8237,12 @@
       <c r="J144" s="5" t="n">
         <v>219.28</v>
       </c>
-      <c r="K144" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L144" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M144" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N144" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O144" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P144" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K144" s="5" t="n"/>
+      <c r="L144" s="5" t="n"/>
+      <c r="M144" s="5" t="n"/>
+      <c r="N144" s="5" t="n"/>
+      <c r="O144" s="5" t="n"/>
+      <c r="P144" s="5" t="n"/>
       <c r="Q144" s="5" t="inlineStr">
         <is>
           <t>D0=224.36; 最新=2026-06-04; 相对D0=-2.26%</t>
@@ -10457,24 +8294,12 @@
       <c r="J145" s="5" t="n">
         <v>65.61</v>
       </c>
-      <c r="K145" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L145" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M145" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N145" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O145" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P145" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K145" s="5" t="n"/>
+      <c r="L145" s="5" t="n"/>
+      <c r="M145" s="5" t="n"/>
+      <c r="N145" s="5" t="n"/>
+      <c r="O145" s="5" t="n"/>
+      <c r="P145" s="5" t="n"/>
       <c r="Q145" s="5" t="inlineStr">
         <is>
           <t>D0=66.89; 最新=2026-06-04; 相对D0=-1.91%</t>
@@ -10526,24 +8351,12 @@
       <c r="J146" s="5" t="n">
         <v>58.49</v>
       </c>
-      <c r="K146" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L146" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M146" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N146" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O146" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P146" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K146" s="5" t="n"/>
+      <c r="L146" s="5" t="n"/>
+      <c r="M146" s="5" t="n"/>
+      <c r="N146" s="5" t="n"/>
+      <c r="O146" s="5" t="n"/>
+      <c r="P146" s="5" t="n"/>
       <c r="Q146" s="5" t="inlineStr">
         <is>
           <t>D0=58.92; 最新=2026-06-04; 相对D0=-0.73%</t>
@@ -10595,24 +8408,6 @@
       <c r="J147" t="n">
         <v>14.61</v>
       </c>
-      <c r="K147" t="n">
-        <v/>
-      </c>
-      <c r="L147" t="n">
-        <v/>
-      </c>
-      <c r="M147" t="n">
-        <v/>
-      </c>
-      <c r="N147" t="n">
-        <v/>
-      </c>
-      <c r="O147" t="n">
-        <v/>
-      </c>
-      <c r="P147" t="n">
-        <v/>
-      </c>
       <c r="Q147" t="inlineStr">
         <is>
           <t>D0=13.89; 最新=2026-06-04; 相对D0=5.18%</t>
@@ -10664,24 +8459,6 @@
       <c r="J148" t="n">
         <v>14.7114</v>
       </c>
-      <c r="K148" t="n">
-        <v/>
-      </c>
-      <c r="L148" t="n">
-        <v/>
-      </c>
-      <c r="M148" t="n">
-        <v/>
-      </c>
-      <c r="N148" t="n">
-        <v/>
-      </c>
-      <c r="O148" t="n">
-        <v/>
-      </c>
-      <c r="P148" t="n">
-        <v/>
-      </c>
       <c r="Q148" t="inlineStr">
         <is>
           <t>D0=15.58; 最新=2026-06-04; 相对D0=-5.58%</t>
@@ -10733,24 +8510,12 @@
       <c r="J149" s="5" t="n">
         <v>17.58</v>
       </c>
-      <c r="K149" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L149" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M149" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N149" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O149" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P149" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K149" s="5" t="n"/>
+      <c r="L149" s="5" t="n"/>
+      <c r="M149" s="5" t="n"/>
+      <c r="N149" s="5" t="n"/>
+      <c r="O149" s="5" t="n"/>
+      <c r="P149" s="5" t="n"/>
       <c r="Q149" s="5" t="inlineStr">
         <is>
           <t>D0=17.62; 最新=2026-06-04; 相对D0=-0.23%</t>
@@ -10802,24 +8567,6 @@
       <c r="J150" t="n">
         <v>320.39</v>
       </c>
-      <c r="K150" t="n">
-        <v/>
-      </c>
-      <c r="L150" t="n">
-        <v/>
-      </c>
-      <c r="M150" t="n">
-        <v/>
-      </c>
-      <c r="N150" t="n">
-        <v/>
-      </c>
-      <c r="O150" t="n">
-        <v/>
-      </c>
-      <c r="P150" t="n">
-        <v/>
-      </c>
       <c r="Q150" t="inlineStr">
         <is>
           <t>D0=323.39; 最新=2026-06-04; 相对D0=-0.93%</t>
@@ -10871,24 +8618,6 @@
       <c r="J151" t="n">
         <v>134.84</v>
       </c>
-      <c r="K151" t="n">
-        <v/>
-      </c>
-      <c r="L151" t="n">
-        <v/>
-      </c>
-      <c r="M151" t="n">
-        <v/>
-      </c>
-      <c r="N151" t="n">
-        <v/>
-      </c>
-      <c r="O151" t="n">
-        <v/>
-      </c>
-      <c r="P151" t="n">
-        <v/>
-      </c>
       <c r="Q151" t="inlineStr">
         <is>
           <t>D0=155.71; 最新=2026-06-04; 相对D0=-13.40%</t>
@@ -10940,24 +8669,12 @@
       <c r="J152" s="5" t="n">
         <v>311.17</v>
       </c>
-      <c r="K152" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L152" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M152" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N152" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O152" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P152" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K152" s="5" t="n"/>
+      <c r="L152" s="5" t="n"/>
+      <c r="M152" s="5" t="n"/>
+      <c r="N152" s="5" t="n"/>
+      <c r="O152" s="5" t="n"/>
+      <c r="P152" s="5" t="n"/>
       <c r="Q152" s="5" t="inlineStr">
         <is>
           <t>D0=315.20; 最新=2026-06-04; 相对D0=-1.28%; 历史重复1次; 重复日期=2026-06-03</t>
@@ -11009,24 +8726,12 @@
       <c r="J153" s="5" t="n">
         <v>115.4564</v>
       </c>
-      <c r="K153" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L153" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M153" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N153" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O153" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P153" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K153" s="5" t="n"/>
+      <c r="L153" s="5" t="n"/>
+      <c r="M153" s="5" t="n"/>
+      <c r="N153" s="5" t="n"/>
+      <c r="O153" s="5" t="n"/>
+      <c r="P153" s="5" t="n"/>
       <c r="Q153" s="5" t="inlineStr">
         <is>
           <t>D0=113.00; 最新=2026-06-04; 相对D0=2.17%</t>
@@ -11078,24 +8783,6 @@
       <c r="J154" t="n">
         <v>108.32</v>
       </c>
-      <c r="K154" t="n">
-        <v/>
-      </c>
-      <c r="L154" t="n">
-        <v/>
-      </c>
-      <c r="M154" t="n">
-        <v/>
-      </c>
-      <c r="N154" t="n">
-        <v/>
-      </c>
-      <c r="O154" t="n">
-        <v/>
-      </c>
-      <c r="P154" t="n">
-        <v/>
-      </c>
       <c r="Q154" t="inlineStr">
         <is>
           <t>D0=118.17; 最新=2026-06-04; 相对D0=-8.34%</t>
@@ -11147,24 +8834,6 @@
       <c r="J155" t="n">
         <v>293.63</v>
       </c>
-      <c r="K155" t="n">
-        <v/>
-      </c>
-      <c r="L155" t="n">
-        <v/>
-      </c>
-      <c r="M155" t="n">
-        <v/>
-      </c>
-      <c r="N155" t="n">
-        <v/>
-      </c>
-      <c r="O155" t="n">
-        <v/>
-      </c>
-      <c r="P155" t="n">
-        <v/>
-      </c>
       <c r="Q155" t="inlineStr">
         <is>
           <t>D0=302.85; 最新=2026-06-04; 相对D0=-3.04%</t>
@@ -11216,24 +8885,12 @@
       <c r="J156" s="5" t="n">
         <v>181.05</v>
       </c>
-      <c r="K156" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L156" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M156" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N156" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O156" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P156" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K156" s="5" t="n"/>
+      <c r="L156" s="5" t="n"/>
+      <c r="M156" s="5" t="n"/>
+      <c r="N156" s="5" t="n"/>
+      <c r="O156" s="5" t="n"/>
+      <c r="P156" s="5" t="n"/>
       <c r="Q156" s="5" t="inlineStr">
         <is>
           <t>D0=187.52; 最新=2026-06-04; 相对D0=-3.45%</t>
@@ -11285,24 +8942,6 @@
       <c r="J157" t="n">
         <v>421.87</v>
       </c>
-      <c r="K157" t="n">
-        <v/>
-      </c>
-      <c r="L157" t="n">
-        <v/>
-      </c>
-      <c r="M157" t="n">
-        <v/>
-      </c>
-      <c r="N157" t="n">
-        <v/>
-      </c>
-      <c r="O157" t="n">
-        <v/>
-      </c>
-      <c r="P157" t="n">
-        <v/>
-      </c>
       <c r="Q157" t="inlineStr">
         <is>
           <t>D0=426.89; 最新=2026-06-04; 相对D0=-1.18%</t>
@@ -11354,24 +8993,12 @@
       <c r="J158" s="5" t="n">
         <v>119.06</v>
       </c>
-      <c r="K158" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L158" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M158" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N158" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O158" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P158" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K158" s="5" t="n"/>
+      <c r="L158" s="5" t="n"/>
+      <c r="M158" s="5" t="n"/>
+      <c r="N158" s="5" t="n"/>
+      <c r="O158" s="5" t="n"/>
+      <c r="P158" s="5" t="n"/>
       <c r="Q158" s="5" t="inlineStr">
         <is>
           <t>D0=116.87; 最新=2026-06-04; 相对D0=1.87%</t>
@@ -11423,24 +9050,12 @@
       <c r="J159" s="5" t="n">
         <v>189.65</v>
       </c>
-      <c r="K159" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L159" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M159" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N159" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O159" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P159" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K159" s="5" t="n"/>
+      <c r="L159" s="5" t="n"/>
+      <c r="M159" s="5" t="n"/>
+      <c r="N159" s="5" t="n"/>
+      <c r="O159" s="5" t="n"/>
+      <c r="P159" s="5" t="n"/>
       <c r="Q159" s="5" t="inlineStr">
         <is>
           <t>D0=187.55; 最新=2026-06-04; 相对D0=1.12%</t>
@@ -11492,24 +9107,6 @@
       <c r="J160" t="n">
         <v>66.75</v>
       </c>
-      <c r="K160" t="n">
-        <v/>
-      </c>
-      <c r="L160" t="n">
-        <v/>
-      </c>
-      <c r="M160" t="n">
-        <v/>
-      </c>
-      <c r="N160" t="n">
-        <v/>
-      </c>
-      <c r="O160" t="n">
-        <v/>
-      </c>
-      <c r="P160" t="n">
-        <v/>
-      </c>
       <c r="Q160" t="inlineStr">
         <is>
           <t>D0=66.47; 最新=2026-06-04; 相对D0=0.42%</t>
@@ -11561,24 +9158,12 @@
       <c r="J161" s="5" t="n">
         <v>47.42</v>
       </c>
-      <c r="K161" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L161" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M161" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N161" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O161" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P161" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K161" s="5" t="n"/>
+      <c r="L161" s="5" t="n"/>
+      <c r="M161" s="5" t="n"/>
+      <c r="N161" s="5" t="n"/>
+      <c r="O161" s="5" t="n"/>
+      <c r="P161" s="5" t="n"/>
       <c r="Q161" s="5" t="inlineStr">
         <is>
           <t>D0=48.66; 最新=2026-06-04; 相对D0=-2.55%</t>
@@ -11630,24 +9215,6 @@
       <c r="J162" t="n">
         <v>68.535</v>
       </c>
-      <c r="K162" t="n">
-        <v/>
-      </c>
-      <c r="L162" t="n">
-        <v/>
-      </c>
-      <c r="M162" t="n">
-        <v/>
-      </c>
-      <c r="N162" t="n">
-        <v/>
-      </c>
-      <c r="O162" t="n">
-        <v/>
-      </c>
-      <c r="P162" t="n">
-        <v/>
-      </c>
       <c r="Q162" t="inlineStr">
         <is>
           <t>D0=72.33; 最新=2026-06-04; 相对D0=-5.25%</t>
@@ -11699,24 +9266,12 @@
       <c r="J163" s="5" t="n">
         <v>140.975</v>
       </c>
-      <c r="K163" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L163" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M163" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N163" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O163" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P163" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K163" s="5" t="n"/>
+      <c r="L163" s="5" t="n"/>
+      <c r="M163" s="5" t="n"/>
+      <c r="N163" s="5" t="n"/>
+      <c r="O163" s="5" t="n"/>
+      <c r="P163" s="5" t="n"/>
       <c r="Q163" s="5" t="inlineStr">
         <is>
           <t>D0=142.92; 最新=2026-06-04; 相对D0=-1.36%</t>
@@ -11768,24 +9323,12 @@
       <c r="J164" s="5" t="n">
         <v>140.775</v>
       </c>
-      <c r="K164" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L164" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M164" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N164" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O164" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P164" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K164" s="5" t="n"/>
+      <c r="L164" s="5" t="n"/>
+      <c r="M164" s="5" t="n"/>
+      <c r="N164" s="5" t="n"/>
+      <c r="O164" s="5" t="n"/>
+      <c r="P164" s="5" t="n"/>
       <c r="Q164" s="5" t="inlineStr">
         <is>
           <t>D0=138.58; 最新=2026-06-04; 相对D0=1.58%</t>
@@ -11837,24 +9380,6 @@
       <c r="J165" t="n">
         <v>417.55</v>
       </c>
-      <c r="K165" t="n">
-        <v/>
-      </c>
-      <c r="L165" t="n">
-        <v/>
-      </c>
-      <c r="M165" t="n">
-        <v/>
-      </c>
-      <c r="N165" t="n">
-        <v/>
-      </c>
-      <c r="O165" t="n">
-        <v/>
-      </c>
-      <c r="P165" t="n">
-        <v/>
-      </c>
       <c r="Q165" t="inlineStr">
         <is>
           <t>D0=417.62; 最新=2026-06-04; 相对D0=-0.02%</t>
@@ -11906,24 +9431,6 @@
       <c r="J166" t="n">
         <v>197.49</v>
       </c>
-      <c r="K166" t="n">
-        <v/>
-      </c>
-      <c r="L166" t="n">
-        <v/>
-      </c>
-      <c r="M166" t="n">
-        <v/>
-      </c>
-      <c r="N166" t="n">
-        <v/>
-      </c>
-      <c r="O166" t="n">
-        <v/>
-      </c>
-      <c r="P166" t="n">
-        <v/>
-      </c>
       <c r="Q166" t="inlineStr">
         <is>
           <t>D0=200.40; 最新=2026-06-04; 相对D0=-1.45%</t>
@@ -11975,24 +9482,12 @@
       <c r="J167" s="5" t="n">
         <v>41.25</v>
       </c>
-      <c r="K167" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L167" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M167" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N167" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O167" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P167" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K167" s="5" t="n"/>
+      <c r="L167" s="5" t="n"/>
+      <c r="M167" s="5" t="n"/>
+      <c r="N167" s="5" t="n"/>
+      <c r="O167" s="5" t="n"/>
+      <c r="P167" s="5" t="n"/>
       <c r="Q167" s="5" t="inlineStr">
         <is>
           <t>D0=40.13; 最新=2026-06-04; 相对D0=2.79%; 历史重复1次; 重复日期=2026-06-03</t>
@@ -12044,24 +9539,6 @@
       <c r="J168" t="n">
         <v>12.64</v>
       </c>
-      <c r="K168" t="n">
-        <v/>
-      </c>
-      <c r="L168" t="n">
-        <v/>
-      </c>
-      <c r="M168" t="n">
-        <v/>
-      </c>
-      <c r="N168" t="n">
-        <v/>
-      </c>
-      <c r="O168" t="n">
-        <v/>
-      </c>
-      <c r="P168" t="n">
-        <v/>
-      </c>
       <c r="Q168" t="inlineStr">
         <is>
           <t>D0=12.72; 最新=2026-06-04; 相对D0=-0.63%</t>
@@ -12113,24 +9590,6 @@
       <c r="J169" t="n">
         <v>11.29</v>
       </c>
-      <c r="K169" t="n">
-        <v/>
-      </c>
-      <c r="L169" t="n">
-        <v/>
-      </c>
-      <c r="M169" t="n">
-        <v/>
-      </c>
-      <c r="N169" t="n">
-        <v/>
-      </c>
-      <c r="O169" t="n">
-        <v/>
-      </c>
-      <c r="P169" t="n">
-        <v/>
-      </c>
       <c r="Q169" t="inlineStr">
         <is>
           <t>D0=11.72; 最新=2026-06-04; 相对D0=-3.67%</t>
@@ -12182,24 +9641,6 @@
       <c r="J170" t="n">
         <v>22.66</v>
       </c>
-      <c r="K170" t="n">
-        <v/>
-      </c>
-      <c r="L170" t="n">
-        <v/>
-      </c>
-      <c r="M170" t="n">
-        <v/>
-      </c>
-      <c r="N170" t="n">
-        <v/>
-      </c>
-      <c r="O170" t="n">
-        <v/>
-      </c>
-      <c r="P170" t="n">
-        <v/>
-      </c>
       <c r="Q170" t="inlineStr">
         <is>
           <t>D0=23.30; 最新=2026-06-04; 相对D0=-2.75%</t>
@@ -12251,24 +9692,12 @@
       <c r="J171" s="5" t="n">
         <v>131.7</v>
       </c>
-      <c r="K171" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L171" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M171" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N171" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O171" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P171" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K171" s="5" t="n"/>
+      <c r="L171" s="5" t="n"/>
+      <c r="M171" s="5" t="n"/>
+      <c r="N171" s="5" t="n"/>
+      <c r="O171" s="5" t="n"/>
+      <c r="P171" s="5" t="n"/>
       <c r="Q171" s="5" t="inlineStr">
         <is>
           <t>D0=138.17; 最新=2026-06-04; 相对D0=-4.68%</t>
@@ -12320,24 +9749,6 @@
       <c r="J172" t="n">
         <v>132.615</v>
       </c>
-      <c r="K172" t="n">
-        <v/>
-      </c>
-      <c r="L172" t="n">
-        <v/>
-      </c>
-      <c r="M172" t="n">
-        <v/>
-      </c>
-      <c r="N172" t="n">
-        <v/>
-      </c>
-      <c r="O172" t="n">
-        <v/>
-      </c>
-      <c r="P172" t="n">
-        <v/>
-      </c>
       <c r="Q172" t="inlineStr">
         <is>
           <t>D0=133.51; 最新=2026-06-04; 相对D0=-0.67%</t>
@@ -12389,24 +9800,6 @@
       <c r="J173" t="n">
         <v>30.305</v>
       </c>
-      <c r="K173" t="n">
-        <v/>
-      </c>
-      <c r="L173" t="n">
-        <v/>
-      </c>
-      <c r="M173" t="n">
-        <v/>
-      </c>
-      <c r="N173" t="n">
-        <v/>
-      </c>
-      <c r="O173" t="n">
-        <v/>
-      </c>
-      <c r="P173" t="n">
-        <v/>
-      </c>
       <c r="Q173" t="inlineStr">
         <is>
           <t>D0=25.86; 最新=2026-06-04; 相对D0=17.19%; 历史重复1次; 重复日期=2026-06-03</t>
@@ -12458,24 +9851,12 @@
       <c r="J174" s="5" t="n">
         <v>65.61</v>
       </c>
-      <c r="K174" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L174" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M174" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N174" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O174" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P174" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K174" s="5" t="n"/>
+      <c r="L174" s="5" t="n"/>
+      <c r="M174" s="5" t="n"/>
+      <c r="N174" s="5" t="n"/>
+      <c r="O174" s="5" t="n"/>
+      <c r="P174" s="5" t="n"/>
       <c r="Q174" s="5" t="inlineStr">
         <is>
           <t>D0=73.47; 最新=2026-06-04; 相对D0=-10.70%</t>
@@ -12527,24 +9908,12 @@
       <c r="J175" s="5" t="n">
         <v>276.586</v>
       </c>
-      <c r="K175" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L175" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M175" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N175" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O175" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P175" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K175" s="5" t="n"/>
+      <c r="L175" s="5" t="n"/>
+      <c r="M175" s="5" t="n"/>
+      <c r="N175" s="5" t="n"/>
+      <c r="O175" s="5" t="n"/>
+      <c r="P175" s="5" t="n"/>
       <c r="Q175" s="5" t="inlineStr">
         <is>
           <t>D0=278.02; 最新=2026-06-04; 相对D0=-0.52%</t>
@@ -12596,24 +9965,6 @@
       <c r="J176" t="n">
         <v>57.47</v>
       </c>
-      <c r="K176" t="n">
-        <v/>
-      </c>
-      <c r="L176" t="n">
-        <v/>
-      </c>
-      <c r="M176" t="n">
-        <v/>
-      </c>
-      <c r="N176" t="n">
-        <v/>
-      </c>
-      <c r="O176" t="n">
-        <v/>
-      </c>
-      <c r="P176" t="n">
-        <v/>
-      </c>
       <c r="Q176" t="inlineStr">
         <is>
           <t>D0=56.89; 最新=2026-06-04; 相对D0=1.02%</t>
@@ -12665,24 +10016,12 @@
       <c r="J177" s="5" t="n">
         <v>57.59</v>
       </c>
-      <c r="K177" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L177" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M177" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N177" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O177" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P177" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K177" s="5" t="n"/>
+      <c r="L177" s="5" t="n"/>
+      <c r="M177" s="5" t="n"/>
+      <c r="N177" s="5" t="n"/>
+      <c r="O177" s="5" t="n"/>
+      <c r="P177" s="5" t="n"/>
       <c r="Q177" s="5" t="inlineStr">
         <is>
           <t>D0=56.56; 最新=2026-06-04; 相对D0=1.82%</t>
@@ -12734,24 +10073,6 @@
       <c r="J178" t="n">
         <v>490.895</v>
       </c>
-      <c r="K178" t="n">
-        <v/>
-      </c>
-      <c r="L178" t="n">
-        <v/>
-      </c>
-      <c r="M178" t="n">
-        <v/>
-      </c>
-      <c r="N178" t="n">
-        <v/>
-      </c>
-      <c r="O178" t="n">
-        <v/>
-      </c>
-      <c r="P178" t="n">
-        <v/>
-      </c>
       <c r="Q178" t="inlineStr">
         <is>
           <t>D0=508.35; 最新=2026-06-04; 相对D0=-3.43%; 历史重复1次; 重复日期=2026-06-03</t>
@@ -12803,24 +10124,6 @@
       <c r="J179" t="n">
         <v>84.91500000000001</v>
       </c>
-      <c r="K179" t="n">
-        <v/>
-      </c>
-      <c r="L179" t="n">
-        <v/>
-      </c>
-      <c r="M179" t="n">
-        <v/>
-      </c>
-      <c r="N179" t="n">
-        <v/>
-      </c>
-      <c r="O179" t="n">
-        <v/>
-      </c>
-      <c r="P179" t="n">
-        <v/>
-      </c>
       <c r="Q179" t="inlineStr">
         <is>
           <t>D0=87.39; 最新=2026-06-04; 相对D0=-2.83%</t>
@@ -12872,24 +10175,12 @@
       <c r="J180" s="5" t="n">
         <v>408.5515</v>
       </c>
-      <c r="K180" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L180" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M180" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N180" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O180" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P180" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K180" s="5" t="n"/>
+      <c r="L180" s="5" t="n"/>
+      <c r="M180" s="5" t="n"/>
+      <c r="N180" s="5" t="n"/>
+      <c r="O180" s="5" t="n"/>
+      <c r="P180" s="5" t="n"/>
       <c r="Q180" s="5" t="inlineStr">
         <is>
           <t>D0=392.62; 最新=2026-06-04; 相对D0=4.06%</t>
@@ -12941,24 +10232,6 @@
       <c r="J181" t="n">
         <v>375.29</v>
       </c>
-      <c r="K181" t="n">
-        <v/>
-      </c>
-      <c r="L181" t="n">
-        <v/>
-      </c>
-      <c r="M181" t="n">
-        <v/>
-      </c>
-      <c r="N181" t="n">
-        <v/>
-      </c>
-      <c r="O181" t="n">
-        <v/>
-      </c>
-      <c r="P181" t="n">
-        <v/>
-      </c>
       <c r="Q181" t="inlineStr">
         <is>
           <t>D0=385.51; 最新=2026-06-04; 相对D0=-2.65%</t>
@@ -13010,24 +10283,6 @@
       <c r="J182" t="n">
         <v>264.605</v>
       </c>
-      <c r="K182" t="n">
-        <v/>
-      </c>
-      <c r="L182" t="n">
-        <v/>
-      </c>
-      <c r="M182" t="n">
-        <v/>
-      </c>
-      <c r="N182" t="n">
-        <v/>
-      </c>
-      <c r="O182" t="n">
-        <v/>
-      </c>
-      <c r="P182" t="n">
-        <v/>
-      </c>
       <c r="Q182" t="inlineStr">
         <is>
           <t>D0=274.71; 最新=2026-06-04; 相对D0=-3.68%; 历史重复1次; 重复日期=2026-06-03</t>
@@ -13079,24 +10334,12 @@
       <c r="J183" s="5" t="n">
         <v>14.315</v>
       </c>
-      <c r="K183" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L183" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M183" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N183" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O183" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P183" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K183" s="5" t="n"/>
+      <c r="L183" s="5" t="n"/>
+      <c r="M183" s="5" t="n"/>
+      <c r="N183" s="5" t="n"/>
+      <c r="O183" s="5" t="n"/>
+      <c r="P183" s="5" t="n"/>
       <c r="Q183" s="5" t="inlineStr">
         <is>
           <t>D0=15.44; 最新=2026-06-04; 相对D0=-7.29%</t>
@@ -13148,24 +10391,12 @@
       <c r="J184" s="5" t="n">
         <v>17.58</v>
       </c>
-      <c r="K184" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L184" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M184" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N184" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O184" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P184" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K184" s="5" t="n"/>
+      <c r="L184" s="5" t="n"/>
+      <c r="M184" s="5" t="n"/>
+      <c r="N184" s="5" t="n"/>
+      <c r="O184" s="5" t="n"/>
+      <c r="P184" s="5" t="n"/>
       <c r="Q184" s="5" t="inlineStr">
         <is>
           <t>D0=19.54; 最新=2026-06-04; 相对D0=-10.03%</t>
@@ -13217,24 +10448,6 @@
       <c r="J185" t="n">
         <v>320.39</v>
       </c>
-      <c r="K185" t="n">
-        <v/>
-      </c>
-      <c r="L185" t="n">
-        <v/>
-      </c>
-      <c r="M185" t="n">
-        <v/>
-      </c>
-      <c r="N185" t="n">
-        <v/>
-      </c>
-      <c r="O185" t="n">
-        <v/>
-      </c>
-      <c r="P185" t="n">
-        <v/>
-      </c>
       <c r="Q185" t="inlineStr">
         <is>
           <t>D0=334.49; 最新=2026-06-04; 相对D0=-4.22%</t>
@@ -13286,24 +10499,6 @@
       <c r="J186" t="n">
         <v>152.85</v>
       </c>
-      <c r="K186" t="n">
-        <v/>
-      </c>
-      <c r="L186" t="n">
-        <v/>
-      </c>
-      <c r="M186" t="n">
-        <v/>
-      </c>
-      <c r="N186" t="n">
-        <v/>
-      </c>
-      <c r="O186" t="n">
-        <v/>
-      </c>
-      <c r="P186" t="n">
-        <v/>
-      </c>
       <c r="Q186" t="inlineStr">
         <is>
           <t>D0=157.97; 最新=2026-06-04; 相对D0=-3.24%</t>
@@ -13355,24 +10550,6 @@
       <c r="J187" t="n">
         <v>51.635</v>
       </c>
-      <c r="K187" t="n">
-        <v/>
-      </c>
-      <c r="L187" t="n">
-        <v/>
-      </c>
-      <c r="M187" t="n">
-        <v/>
-      </c>
-      <c r="N187" t="n">
-        <v/>
-      </c>
-      <c r="O187" t="n">
-        <v/>
-      </c>
-      <c r="P187" t="n">
-        <v/>
-      </c>
       <c r="Q187" t="inlineStr">
         <is>
           <t>D0=51.52; 最新=2026-06-04; 相对D0=0.22%</t>
@@ -13424,24 +10601,12 @@
       <c r="J188" s="5" t="n">
         <v>58.925</v>
       </c>
-      <c r="K188" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L188" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M188" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N188" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O188" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P188" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K188" s="5" t="n"/>
+      <c r="L188" s="5" t="n"/>
+      <c r="M188" s="5" t="n"/>
+      <c r="N188" s="5" t="n"/>
+      <c r="O188" s="5" t="n"/>
+      <c r="P188" s="5" t="n"/>
       <c r="Q188" s="5" t="inlineStr">
         <is>
           <t>D0=57.96; 最新=2026-06-04; 相对D0=1.66%; 历史重复1次; 重复日期=2026-06-03</t>
@@ -13493,24 +10658,6 @@
       <c r="J189" t="n">
         <v>52.135</v>
       </c>
-      <c r="K189" t="n">
-        <v/>
-      </c>
-      <c r="L189" t="n">
-        <v/>
-      </c>
-      <c r="M189" t="n">
-        <v/>
-      </c>
-      <c r="N189" t="n">
-        <v/>
-      </c>
-      <c r="O189" t="n">
-        <v/>
-      </c>
-      <c r="P189" t="n">
-        <v/>
-      </c>
       <c r="Q189" t="inlineStr">
         <is>
           <t>D0=51.46; 最新=2026-06-04; 相对D0=1.31%</t>
@@ -13562,24 +10709,6 @@
       <c r="J190" t="n">
         <v>198.7336</v>
       </c>
-      <c r="K190" t="n">
-        <v/>
-      </c>
-      <c r="L190" t="n">
-        <v/>
-      </c>
-      <c r="M190" t="n">
-        <v/>
-      </c>
-      <c r="N190" t="n">
-        <v/>
-      </c>
-      <c r="O190" t="n">
-        <v/>
-      </c>
-      <c r="P190" t="n">
-        <v/>
-      </c>
       <c r="Q190" t="inlineStr">
         <is>
           <t>D0=184.07; 最新=2026-06-04; 相对D0=7.97%</t>
@@ -13631,24 +10760,12 @@
       <c r="J191" s="5" t="n">
         <v>311.17</v>
       </c>
-      <c r="K191" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L191" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M191" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N191" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O191" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P191" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K191" s="5" t="n"/>
+      <c r="L191" s="5" t="n"/>
+      <c r="M191" s="5" t="n"/>
+      <c r="N191" s="5" t="n"/>
+      <c r="O191" s="5" t="n"/>
+      <c r="P191" s="5" t="n"/>
       <c r="Q191" s="5" t="inlineStr">
         <is>
           <t>D0=310.26; 最新=2026-06-04; 相对D0=0.29%</t>
@@ -13700,24 +10817,6 @@
       <c r="J192" t="n">
         <v>284.365</v>
       </c>
-      <c r="K192" t="n">
-        <v/>
-      </c>
-      <c r="L192" t="n">
-        <v/>
-      </c>
-      <c r="M192" t="n">
-        <v/>
-      </c>
-      <c r="N192" t="n">
-        <v/>
-      </c>
-      <c r="O192" t="n">
-        <v/>
-      </c>
-      <c r="P192" t="n">
-        <v/>
-      </c>
       <c r="Q192" t="inlineStr">
         <is>
           <t>D0=282.27; 最新=2026-06-04; 相对D0=0.74%</t>
@@ -13769,24 +10868,12 @@
       <c r="J193" s="5" t="n">
         <v>119.06</v>
       </c>
-      <c r="K193" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L193" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M193" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N193" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O193" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P193" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K193" s="5" t="n"/>
+      <c r="L193" s="5" t="n"/>
+      <c r="M193" s="5" t="n"/>
+      <c r="N193" s="5" t="n"/>
+      <c r="O193" s="5" t="n"/>
+      <c r="P193" s="5" t="n"/>
       <c r="Q193" s="5" t="inlineStr">
         <is>
           <t>D0=119.05; 最新=2026-06-04; 相对D0=0.01%</t>
@@ -13838,24 +10925,6 @@
       <c r="J194" t="n">
         <v>121.42</v>
       </c>
-      <c r="K194" t="n">
-        <v/>
-      </c>
-      <c r="L194" t="n">
-        <v/>
-      </c>
-      <c r="M194" t="n">
-        <v/>
-      </c>
-      <c r="N194" t="n">
-        <v/>
-      </c>
-      <c r="O194" t="n">
-        <v/>
-      </c>
-      <c r="P194" t="n">
-        <v/>
-      </c>
       <c r="Q194" t="inlineStr">
         <is>
           <t>D0=121.04; 最新=2026-06-04; 相对D0=0.31%</t>
@@ -13907,24 +10976,12 @@
       <c r="J195" s="5" t="n">
         <v>41.25</v>
       </c>
-      <c r="K195" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L195" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M195" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N195" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O195" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P195" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K195" s="5" t="n"/>
+      <c r="L195" s="5" t="n"/>
+      <c r="M195" s="5" t="n"/>
+      <c r="N195" s="5" t="n"/>
+      <c r="O195" s="5" t="n"/>
+      <c r="P195" s="5" t="n"/>
       <c r="Q195" s="5" t="inlineStr">
         <is>
           <t>D0=41.03; 最新=2026-06-04; 相对D0=0.54%</t>
@@ -13976,24 +11033,6 @@
       <c r="J196" t="n">
         <v>51.52</v>
       </c>
-      <c r="K196" t="n">
-        <v/>
-      </c>
-      <c r="L196" t="n">
-        <v/>
-      </c>
-      <c r="M196" t="n">
-        <v/>
-      </c>
-      <c r="N196" t="n">
-        <v/>
-      </c>
-      <c r="O196" t="n">
-        <v/>
-      </c>
-      <c r="P196" t="n">
-        <v/>
-      </c>
       <c r="Q196" t="inlineStr">
         <is>
           <t>D0=50.01; 最新=2026-06-04; 相对D0=3.02%</t>
@@ -14045,24 +11084,6 @@
       <c r="J197" t="n">
         <v>507.79</v>
       </c>
-      <c r="K197" t="n">
-        <v/>
-      </c>
-      <c r="L197" t="n">
-        <v/>
-      </c>
-      <c r="M197" t="n">
-        <v/>
-      </c>
-      <c r="N197" t="n">
-        <v/>
-      </c>
-      <c r="O197" t="n">
-        <v/>
-      </c>
-      <c r="P197" t="n">
-        <v/>
-      </c>
       <c r="Q197" t="inlineStr">
         <is>
           <t>D0=507.57; 最新=2026-06-04; 相对D0=0.04%</t>
@@ -14114,24 +11135,12 @@
       <c r="J198" s="5" t="n">
         <v>629.355</v>
       </c>
-      <c r="K198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O198" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P198" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K198" s="5" t="n"/>
+      <c r="L198" s="5" t="n"/>
+      <c r="M198" s="5" t="n"/>
+      <c r="N198" s="5" t="n"/>
+      <c r="O198" s="5" t="n"/>
+      <c r="P198" s="5" t="n"/>
       <c r="Q198" s="5" t="inlineStr">
         <is>
           <t>D0=622.98; 最新=2026-06-04; 相对D0=1.02%</t>
@@ -14183,24 +11192,6 @@
       <c r="J199" t="n">
         <v>22.66</v>
       </c>
-      <c r="K199" t="n">
-        <v/>
-      </c>
-      <c r="L199" t="n">
-        <v/>
-      </c>
-      <c r="M199" t="n">
-        <v/>
-      </c>
-      <c r="N199" t="n">
-        <v/>
-      </c>
-      <c r="O199" t="n">
-        <v/>
-      </c>
-      <c r="P199" t="n">
-        <v/>
-      </c>
       <c r="Q199" t="inlineStr">
         <is>
           <t>D0=23.30; 最新=2026-06-04; 相对D0=-2.75%</t>
@@ -14252,24 +11243,6 @@
       <c r="J200" t="n">
         <v>68.81999999999999</v>
       </c>
-      <c r="K200" t="n">
-        <v/>
-      </c>
-      <c r="L200" t="n">
-        <v/>
-      </c>
-      <c r="M200" t="n">
-        <v/>
-      </c>
-      <c r="N200" t="n">
-        <v/>
-      </c>
-      <c r="O200" t="n">
-        <v/>
-      </c>
-      <c r="P200" t="n">
-        <v/>
-      </c>
       <c r="Q200" t="inlineStr">
         <is>
           <t>D0=68.81; 最新=2026-06-04; 相对D0=0.01%</t>
@@ -14321,24 +11294,6 @@
       <c r="J201" t="n">
         <v>30.305</v>
       </c>
-      <c r="K201" t="n">
-        <v/>
-      </c>
-      <c r="L201" t="n">
-        <v/>
-      </c>
-      <c r="M201" t="n">
-        <v/>
-      </c>
-      <c r="N201" t="n">
-        <v/>
-      </c>
-      <c r="O201" t="n">
-        <v/>
-      </c>
-      <c r="P201" t="n">
-        <v/>
-      </c>
       <c r="Q201" t="inlineStr">
         <is>
           <t>D0=30.84; 最新=2026-06-04; 相对D0=-1.73%</t>
@@ -14390,24 +11345,6 @@
       <c r="J202" t="n">
         <v>148.525</v>
       </c>
-      <c r="K202" t="n">
-        <v/>
-      </c>
-      <c r="L202" t="n">
-        <v/>
-      </c>
-      <c r="M202" t="n">
-        <v/>
-      </c>
-      <c r="N202" t="n">
-        <v/>
-      </c>
-      <c r="O202" t="n">
-        <v/>
-      </c>
-      <c r="P202" t="n">
-        <v/>
-      </c>
       <c r="Q202" t="inlineStr">
         <is>
           <t>D0=146.47; 最新=2026-06-04; 相对D0=1.40%</t>
@@ -14459,24 +11396,6 @@
       <c r="J203" t="n">
         <v>490.895</v>
       </c>
-      <c r="K203" t="n">
-        <v/>
-      </c>
-      <c r="L203" t="n">
-        <v/>
-      </c>
-      <c r="M203" t="n">
-        <v/>
-      </c>
-      <c r="N203" t="n">
-        <v/>
-      </c>
-      <c r="O203" t="n">
-        <v/>
-      </c>
-      <c r="P203" t="n">
-        <v/>
-      </c>
       <c r="Q203" t="inlineStr">
         <is>
           <t>D0=498.02; 最新=2026-06-04; 相对D0=-1.43%</t>
@@ -14528,24 +11447,6 @@
       <c r="J204" t="n">
         <v>91.06</v>
       </c>
-      <c r="K204" t="n">
-        <v/>
-      </c>
-      <c r="L204" t="n">
-        <v/>
-      </c>
-      <c r="M204" t="n">
-        <v/>
-      </c>
-      <c r="N204" t="n">
-        <v/>
-      </c>
-      <c r="O204" t="n">
-        <v/>
-      </c>
-      <c r="P204" t="n">
-        <v/>
-      </c>
       <c r="Q204" t="inlineStr">
         <is>
           <t>D0=90.49; 最新=2026-06-04; 相对D0=0.63%</t>
@@ -14597,24 +11498,6 @@
       <c r="J205" t="n">
         <v>264.605</v>
       </c>
-      <c r="K205" t="n">
-        <v/>
-      </c>
-      <c r="L205" t="n">
-        <v/>
-      </c>
-      <c r="M205" t="n">
-        <v/>
-      </c>
-      <c r="N205" t="n">
-        <v/>
-      </c>
-      <c r="O205" t="n">
-        <v/>
-      </c>
-      <c r="P205" t="n">
-        <v/>
-      </c>
       <c r="Q205" t="inlineStr">
         <is>
           <t>D0=267.91; 最新=2026-06-04; 相对D0=-1.23%</t>
@@ -14666,24 +11549,6 @@
       <c r="J206" t="n">
         <v>397.02</v>
       </c>
-      <c r="K206" t="n">
-        <v/>
-      </c>
-      <c r="L206" t="n">
-        <v/>
-      </c>
-      <c r="M206" t="n">
-        <v/>
-      </c>
-      <c r="N206" t="n">
-        <v/>
-      </c>
-      <c r="O206" t="n">
-        <v/>
-      </c>
-      <c r="P206" t="n">
-        <v/>
-      </c>
       <c r="Q206" t="inlineStr">
         <is>
           <t>D0=377.00; 最新=2026-06-04; 相对D0=5.31%</t>
@@ -14735,24 +11600,12 @@
       <c r="J207" s="5" t="n">
         <v>58.925</v>
       </c>
-      <c r="K207" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L207" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M207" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N207" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O207" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P207" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K207" s="5" t="n"/>
+      <c r="L207" s="5" t="n"/>
+      <c r="M207" s="5" t="n"/>
+      <c r="N207" s="5" t="n"/>
+      <c r="O207" s="5" t="n"/>
+      <c r="P207" s="5" t="n"/>
       <c r="Q207" s="5" t="inlineStr">
         <is>
           <t>D0=58.71; 最新=2026-06-04; 相对D0=0.37%</t>
@@ -14804,24 +11657,6 @@
       <c r="J208" t="n">
         <v>43.825</v>
       </c>
-      <c r="K208" t="n">
-        <v/>
-      </c>
-      <c r="L208" t="n">
-        <v/>
-      </c>
-      <c r="M208" t="n">
-        <v/>
-      </c>
-      <c r="N208" t="n">
-        <v/>
-      </c>
-      <c r="O208" t="n">
-        <v/>
-      </c>
-      <c r="P208" t="n">
-        <v/>
-      </c>
       <c r="Q208" t="inlineStr">
         <is>
           <t>D0=43.71; 最新=2026-06-04; 相对D0=0.26%</t>
@@ -15058,24 +11893,6 @@
       <c r="J220" t="n">
         <v>417.625</v>
       </c>
-      <c r="K220" t="n">
-        <v/>
-      </c>
-      <c r="L220" t="n">
-        <v/>
-      </c>
-      <c r="M220" t="n">
-        <v/>
-      </c>
-      <c r="N220" t="n">
-        <v/>
-      </c>
-      <c r="O220" t="n">
-        <v/>
-      </c>
-      <c r="P220" t="n">
-        <v/>
-      </c>
       <c r="Q220" t="inlineStr">
         <is>
           <t>D0=417.62; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式卖出 | 预警卖出)</t>
@@ -15127,24 +11944,6 @@
       <c r="J221" t="n">
         <v>88.44</v>
       </c>
-      <c r="K221" t="n">
-        <v/>
-      </c>
-      <c r="L221" t="n">
-        <v/>
-      </c>
-      <c r="M221" t="n">
-        <v/>
-      </c>
-      <c r="N221" t="n">
-        <v/>
-      </c>
-      <c r="O221" t="n">
-        <v/>
-      </c>
-      <c r="P221" t="n">
-        <v/>
-      </c>
       <c r="Q221" t="inlineStr">
         <is>
           <t>D0=88.44; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式卖出 | 预警卖出)</t>
@@ -15196,24 +11995,6 @@
       <c r="J222" t="n">
         <v>61.61</v>
       </c>
-      <c r="K222" t="n">
-        <v/>
-      </c>
-      <c r="L222" t="n">
-        <v/>
-      </c>
-      <c r="M222" t="n">
-        <v/>
-      </c>
-      <c r="N222" t="n">
-        <v/>
-      </c>
-      <c r="O222" t="n">
-        <v/>
-      </c>
-      <c r="P222" t="n">
-        <v/>
-      </c>
       <c r="Q222" t="inlineStr">
         <is>
           <t>D0=61.61; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式卖出 | 预警卖出)</t>
@@ -15265,24 +12046,6 @@
       <c r="J223" t="n">
         <v>22.67</v>
       </c>
-      <c r="K223" t="n">
-        <v/>
-      </c>
-      <c r="L223" t="n">
-        <v/>
-      </c>
-      <c r="M223" t="n">
-        <v/>
-      </c>
-      <c r="N223" t="n">
-        <v/>
-      </c>
-      <c r="O223" t="n">
-        <v/>
-      </c>
-      <c r="P223" t="n">
-        <v/>
-      </c>
       <c r="Q223" t="inlineStr">
         <is>
           <t>D0=22.67; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式卖出)</t>
@@ -15334,24 +12097,6 @@
       <c r="J224" t="n">
         <v>105.1</v>
       </c>
-      <c r="K224" t="n">
-        <v/>
-      </c>
-      <c r="L224" t="n">
-        <v/>
-      </c>
-      <c r="M224" t="n">
-        <v/>
-      </c>
-      <c r="N224" t="n">
-        <v/>
-      </c>
-      <c r="O224" t="n">
-        <v/>
-      </c>
-      <c r="P224" t="n">
-        <v/>
-      </c>
       <c r="Q224" t="inlineStr">
         <is>
           <t>D0=105.10; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式卖出)</t>
@@ -15403,24 +12148,12 @@
       <c r="J225" s="5" t="n">
         <v>375.29</v>
       </c>
-      <c r="K225" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L225" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M225" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N225" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O225" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P225" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K225" s="5" t="n"/>
+      <c r="L225" s="5" t="n"/>
+      <c r="M225" s="5" t="n"/>
+      <c r="N225" s="5" t="n"/>
+      <c r="O225" s="5" t="n"/>
+      <c r="P225" s="5" t="n"/>
       <c r="Q225" s="5" t="inlineStr">
         <is>
           <t>D0=375.29; 最新=2026-06-04; 相对D0=0.00%; 本次触发=2026-06-04(正式卖出)</t>
@@ -15472,24 +12205,12 @@
       <c r="J226" s="5" t="n">
         <v>41.25</v>
       </c>
-      <c r="K226" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L226" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M226" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N226" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O226" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P226" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K226" s="5" t="n"/>
+      <c r="L226" s="5" t="n"/>
+      <c r="M226" s="5" t="n"/>
+      <c r="N226" s="5" t="n"/>
+      <c r="O226" s="5" t="n"/>
+      <c r="P226" s="5" t="n"/>
       <c r="Q226" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-06-04; 相对D0=-0.53%</t>
@@ -15510,7 +12231,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -15536,24 +12256,6 @@
       </c>
       <c r="J227" t="n">
         <v>91.45</v>
-      </c>
-      <c r="K227" t="n">
-        <v/>
-      </c>
-      <c r="L227" t="n">
-        <v/>
-      </c>
-      <c r="M227" t="n">
-        <v/>
-      </c>
-      <c r="N227" t="n">
-        <v/>
-      </c>
-      <c r="O227" t="n">
-        <v/>
-      </c>
-      <c r="P227" t="n">
-        <v/>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
@@ -15606,24 +12308,12 @@
       <c r="J228" s="5" t="n">
         <v>189.65</v>
       </c>
-      <c r="K228" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L228" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M228" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N228" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O228" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P228" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K228" s="5" t="n"/>
+      <c r="L228" s="5" t="n"/>
+      <c r="M228" s="5" t="n"/>
+      <c r="N228" s="5" t="n"/>
+      <c r="O228" s="5" t="n"/>
+      <c r="P228" s="5" t="n"/>
       <c r="Q228" s="5" t="inlineStr">
         <is>
           <t>D0=184.71; 最新=2026-06-04; 相对D0=2.67%</t>
@@ -15675,24 +12365,12 @@
       <c r="J229" s="5" t="n">
         <v>140.74</v>
       </c>
-      <c r="K229" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L229" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M229" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N229" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O229" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P229" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K229" s="5" t="n"/>
+      <c r="L229" s="5" t="n"/>
+      <c r="M229" s="5" t="n"/>
+      <c r="N229" s="5" t="n"/>
+      <c r="O229" s="5" t="n"/>
+      <c r="P229" s="5" t="n"/>
       <c r="Q229" s="5" t="inlineStr">
         <is>
           <t>D0=136.20; 最新=2026-06-04; 相对D0=3.33%</t>
@@ -15744,24 +12422,6 @@
       <c r="J230" t="n">
         <v>379.47</v>
       </c>
-      <c r="K230" t="n">
-        <v/>
-      </c>
-      <c r="L230" t="n">
-        <v/>
-      </c>
-      <c r="M230" t="n">
-        <v/>
-      </c>
-      <c r="N230" t="n">
-        <v/>
-      </c>
-      <c r="O230" t="n">
-        <v/>
-      </c>
-      <c r="P230" t="n">
-        <v/>
-      </c>
       <c r="Q230" t="inlineStr">
         <is>
           <t>D0=307.35; 最新=2026-06-04; 相对D0=23.47%</t>
@@ -15813,24 +12473,12 @@
       <c r="J231" s="5" t="n">
         <v>58.48</v>
       </c>
-      <c r="K231" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L231" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M231" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N231" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O231" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P231" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K231" s="5" t="n"/>
+      <c r="L231" s="5" t="n"/>
+      <c r="M231" s="5" t="n"/>
+      <c r="N231" s="5" t="n"/>
+      <c r="O231" s="5" t="n"/>
+      <c r="P231" s="5" t="n"/>
       <c r="Q231" s="5" t="inlineStr">
         <is>
           <t>D0=57.46; 最新=2026-06-04; 相对D0=1.78%</t>
@@ -15882,24 +12530,12 @@
       <c r="J232" s="5" t="n">
         <v>14.62</v>
       </c>
-      <c r="K232" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L232" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M232" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N232" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O232" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P232" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K232" s="5" t="n"/>
+      <c r="L232" s="5" t="n"/>
+      <c r="M232" s="5" t="n"/>
+      <c r="N232" s="5" t="n"/>
+      <c r="O232" s="5" t="n"/>
+      <c r="P232" s="5" t="n"/>
       <c r="Q232" s="5" t="inlineStr">
         <is>
           <t>D0=13.35; 最新=2026-06-04; 相对D0=9.51%</t>
@@ -15951,24 +12587,12 @@
       <c r="J233" s="5" t="n">
         <v>58.925</v>
       </c>
-      <c r="K233" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L233" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M233" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N233" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O233" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P233" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K233" s="5" t="n"/>
+      <c r="L233" s="5" t="n"/>
+      <c r="M233" s="5" t="n"/>
+      <c r="N233" s="5" t="n"/>
+      <c r="O233" s="5" t="n"/>
+      <c r="P233" s="5" t="n"/>
       <c r="Q233" s="5" t="inlineStr">
         <is>
           <t>D0=57.85; 最新=2026-06-04; 相对D0=1.86%</t>
@@ -16020,24 +12644,12 @@
       <c r="J234" s="5" t="n">
         <v>57.59</v>
       </c>
-      <c r="K234" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L234" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M234" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N234" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O234" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P234" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K234" s="5" t="n"/>
+      <c r="L234" s="5" t="n"/>
+      <c r="M234" s="5" t="n"/>
+      <c r="N234" s="5" t="n"/>
+      <c r="O234" s="5" t="n"/>
+      <c r="P234" s="5" t="n"/>
       <c r="Q234" s="5" t="inlineStr">
         <is>
           <t>D0=56.50; 最新=2026-06-04; 相对D0=1.93%</t>
@@ -16089,24 +12701,6 @@
       <c r="J235" t="n">
         <v>134.84</v>
       </c>
-      <c r="K235" t="n">
-        <v/>
-      </c>
-      <c r="L235" t="n">
-        <v/>
-      </c>
-      <c r="M235" t="n">
-        <v/>
-      </c>
-      <c r="N235" t="n">
-        <v/>
-      </c>
-      <c r="O235" t="n">
-        <v/>
-      </c>
-      <c r="P235" t="n">
-        <v/>
-      </c>
       <c r="Q235" t="inlineStr">
         <is>
           <t>D0=126.41; 最新=2026-06-04; 相对D0=6.67%</t>
@@ -16158,24 +12752,12 @@
       <c r="J236" s="5" t="n">
         <v>109.92</v>
       </c>
-      <c r="K236" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L236" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M236" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N236" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O236" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P236" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K236" s="5" t="n"/>
+      <c r="L236" s="5" t="n"/>
+      <c r="M236" s="5" t="n"/>
+      <c r="N236" s="5" t="n"/>
+      <c r="O236" s="5" t="n"/>
+      <c r="P236" s="5" t="n"/>
       <c r="Q236" s="5" t="inlineStr">
         <is>
           <t>D0=115.70; 最新=2026-06-04; 相对D0=-5.00%</t>
@@ -16227,24 +12809,12 @@
       <c r="J237" s="5" t="n">
         <v>264.2</v>
       </c>
-      <c r="K237" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L237" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M237" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N237" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O237" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P237" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K237" s="5" t="n"/>
+      <c r="L237" s="5" t="n"/>
+      <c r="M237" s="5" t="n"/>
+      <c r="N237" s="5" t="n"/>
+      <c r="O237" s="5" t="n"/>
+      <c r="P237" s="5" t="n"/>
       <c r="Q237" s="5" t="inlineStr">
         <is>
           <t>D0=286.31; 最新=2026-06-04; 相对D0=-7.72%</t>
@@ -16296,24 +12866,12 @@
       <c r="J238" s="5" t="n">
         <v>197.47</v>
       </c>
-      <c r="K238" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L238" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M238" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N238" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O238" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P238" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K238" s="5" t="n"/>
+      <c r="L238" s="5" t="n"/>
+      <c r="M238" s="5" t="n"/>
+      <c r="N238" s="5" t="n"/>
+      <c r="O238" s="5" t="n"/>
+      <c r="P238" s="5" t="n"/>
       <c r="Q238" s="5" t="inlineStr">
         <is>
           <t>D0=182.97; 最新=2026-06-04; 相对D0=7.92%</t>
@@ -16365,24 +12923,6 @@
       <c r="J239" t="n">
         <v>490.895</v>
       </c>
-      <c r="K239" t="n">
-        <v/>
-      </c>
-      <c r="L239" t="n">
-        <v/>
-      </c>
-      <c r="M239" t="n">
-        <v/>
-      </c>
-      <c r="N239" t="n">
-        <v/>
-      </c>
-      <c r="O239" t="n">
-        <v/>
-      </c>
-      <c r="P239" t="n">
-        <v/>
-      </c>
       <c r="Q239" t="inlineStr">
         <is>
           <t>D0=480.64; 最新=2026-06-04; 相对D0=2.13%</t>
@@ -16434,24 +12974,12 @@
       <c r="J240" s="5" t="n">
         <v>115.4564</v>
       </c>
-      <c r="K240" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L240" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M240" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N240" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O240" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P240" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K240" s="5" t="n"/>
+      <c r="L240" s="5" t="n"/>
+      <c r="M240" s="5" t="n"/>
+      <c r="N240" s="5" t="n"/>
+      <c r="O240" s="5" t="n"/>
+      <c r="P240" s="5" t="n"/>
       <c r="Q240" s="5" t="inlineStr">
         <is>
           <t>D0=92.33; 最新=2026-06-04; 相对D0=25.05%</t>
@@ -16503,24 +13031,12 @@
       <c r="J241" s="5" t="n">
         <v>75.3</v>
       </c>
-      <c r="K241" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L241" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M241" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N241" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O241" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P241" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K241" s="5" t="n"/>
+      <c r="L241" s="5" t="n"/>
+      <c r="M241" s="5" t="n"/>
+      <c r="N241" s="5" t="n"/>
+      <c r="O241" s="5" t="n"/>
+      <c r="P241" s="5" t="n"/>
       <c r="Q241" s="5" t="inlineStr">
         <is>
           <t>D0=69.56; 最新=2026-06-04; 相对D0=8.25%</t>
@@ -16572,24 +13088,6 @@
       <c r="J242" t="n">
         <v>293.81</v>
       </c>
-      <c r="K242" t="n">
-        <v/>
-      </c>
-      <c r="L242" t="n">
-        <v/>
-      </c>
-      <c r="M242" t="n">
-        <v/>
-      </c>
-      <c r="N242" t="n">
-        <v/>
-      </c>
-      <c r="O242" t="n">
-        <v/>
-      </c>
-      <c r="P242" t="n">
-        <v/>
-      </c>
       <c r="Q242" t="inlineStr">
         <is>
           <t>D0=285.00; 最新=2026-06-04; 相对D0=3.09%</t>
@@ -16641,24 +13139,12 @@
       <c r="J243" s="5" t="n">
         <v>181.05</v>
       </c>
-      <c r="K243" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L243" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M243" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N243" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O243" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P243" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K243" s="5" t="n"/>
+      <c r="L243" s="5" t="n"/>
+      <c r="M243" s="5" t="n"/>
+      <c r="N243" s="5" t="n"/>
+      <c r="O243" s="5" t="n"/>
+      <c r="P243" s="5" t="n"/>
       <c r="Q243" s="5" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-04; 相对D0=5.47%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -16710,24 +13196,12 @@
       <c r="J244" s="5" t="n">
         <v>421.87</v>
       </c>
-      <c r="K244" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L244" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M244" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N244" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O244" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P244" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K244" s="5" t="n"/>
+      <c r="L244" s="5" t="n"/>
+      <c r="M244" s="5" t="n"/>
+      <c r="N244" s="5" t="n"/>
+      <c r="O244" s="5" t="n"/>
+      <c r="P244" s="5" t="n"/>
       <c r="Q244" s="5" t="inlineStr">
         <is>
           <t>D0=361.47; 最新=2026-06-04; 相对D0=16.71%</t>
@@ -16779,24 +13253,6 @@
       <c r="J245" t="n">
         <v>26.23</v>
       </c>
-      <c r="K245" t="n">
-        <v/>
-      </c>
-      <c r="L245" t="n">
-        <v/>
-      </c>
-      <c r="M245" t="n">
-        <v/>
-      </c>
-      <c r="N245" t="n">
-        <v/>
-      </c>
-      <c r="O245" t="n">
-        <v/>
-      </c>
-      <c r="P245" t="n">
-        <v/>
-      </c>
       <c r="Q245" t="inlineStr">
         <is>
           <t>D0=18.88; 最新=2026-06-04; 相对D0=38.93%</t>
@@ -16848,24 +13304,6 @@
       <c r="J246" t="n">
         <v>111.2801</v>
       </c>
-      <c r="K246" t="n">
-        <v/>
-      </c>
-      <c r="L246" t="n">
-        <v/>
-      </c>
-      <c r="M246" t="n">
-        <v/>
-      </c>
-      <c r="N246" t="n">
-        <v/>
-      </c>
-      <c r="O246" t="n">
-        <v/>
-      </c>
-      <c r="P246" t="n">
-        <v/>
-      </c>
       <c r="Q246" t="inlineStr">
         <is>
           <t>D0=114.68; 最新=2026-06-04; 相对D0=-2.96%</t>
@@ -16917,24 +13355,12 @@
       <c r="J247" s="5" t="n">
         <v>132.615</v>
       </c>
-      <c r="K247" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L247" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M247" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N247" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O247" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P247" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K247" s="5" t="n"/>
+      <c r="L247" s="5" t="n"/>
+      <c r="M247" s="5" t="n"/>
+      <c r="N247" s="5" t="n"/>
+      <c r="O247" s="5" t="n"/>
+      <c r="P247" s="5" t="n"/>
       <c r="Q247" s="5" t="inlineStr">
         <is>
           <t>D0=134.08; 最新=2026-06-04; 相对D0=-1.09%</t>
@@ -16986,24 +13412,12 @@
       <c r="J248" s="5" t="n">
         <v>264.605</v>
       </c>
-      <c r="K248" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L248" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M248" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N248" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O248" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P248" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K248" s="5" t="n"/>
+      <c r="L248" s="5" t="n"/>
+      <c r="M248" s="5" t="n"/>
+      <c r="N248" s="5" t="n"/>
+      <c r="O248" s="5" t="n"/>
+      <c r="P248" s="5" t="n"/>
       <c r="Q248" s="5" t="inlineStr">
         <is>
           <t>D0=255.23; 最新=2026-06-04; 相对D0=3.67%</t>
@@ -17055,24 +13469,6 @@
       <c r="J249" t="n">
         <v>108.41</v>
       </c>
-      <c r="K249" t="n">
-        <v/>
-      </c>
-      <c r="L249" t="n">
-        <v/>
-      </c>
-      <c r="M249" t="n">
-        <v/>
-      </c>
-      <c r="N249" t="n">
-        <v/>
-      </c>
-      <c r="O249" t="n">
-        <v/>
-      </c>
-      <c r="P249" t="n">
-        <v/>
-      </c>
       <c r="Q249" t="inlineStr">
         <is>
           <t>D0=105.65; 最新=2026-06-04; 相对D0=2.61%</t>
@@ -17124,24 +13520,12 @@
       <c r="J250" s="5" t="n">
         <v>181.05</v>
       </c>
-      <c r="K250" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L250" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M250" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N250" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O250" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P250" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K250" s="5" t="n"/>
+      <c r="L250" s="5" t="n"/>
+      <c r="M250" s="5" t="n"/>
+      <c r="N250" s="5" t="n"/>
+      <c r="O250" s="5" t="n"/>
+      <c r="P250" s="5" t="n"/>
       <c r="Q250" s="5" t="inlineStr">
         <is>
           <t>D0=163.09; 最新=2026-06-04; 相对D0=11.01%</t>
@@ -17193,24 +13577,6 @@
       <c r="J251" t="n">
         <v>66.76000000000001</v>
       </c>
-      <c r="K251" t="n">
-        <v/>
-      </c>
-      <c r="L251" t="n">
-        <v/>
-      </c>
-      <c r="M251" t="n">
-        <v/>
-      </c>
-      <c r="N251" t="n">
-        <v/>
-      </c>
-      <c r="O251" t="n">
-        <v/>
-      </c>
-      <c r="P251" t="n">
-        <v/>
-      </c>
       <c r="Q251" t="inlineStr">
         <is>
           <t>D0=64.61; 最新=2026-06-04; 相对D0=3.33%</t>
@@ -17262,24 +13628,12 @@
       <c r="J252" s="5" t="n">
         <v>140.975</v>
       </c>
-      <c r="K252" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L252" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M252" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N252" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O252" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P252" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K252" s="5" t="n"/>
+      <c r="L252" s="5" t="n"/>
+      <c r="M252" s="5" t="n"/>
+      <c r="N252" s="5" t="n"/>
+      <c r="O252" s="5" t="n"/>
+      <c r="P252" s="5" t="n"/>
       <c r="Q252" s="5" t="inlineStr">
         <is>
           <t>D0=135.73; 最新=2026-06-04; 相对D0=3.86%</t>
@@ -17331,24 +13685,6 @@
       <c r="J253" t="n">
         <v>629.34</v>
       </c>
-      <c r="K253" t="n">
-        <v/>
-      </c>
-      <c r="L253" t="n">
-        <v/>
-      </c>
-      <c r="M253" t="n">
-        <v/>
-      </c>
-      <c r="N253" t="n">
-        <v/>
-      </c>
-      <c r="O253" t="n">
-        <v/>
-      </c>
-      <c r="P253" t="n">
-        <v/>
-      </c>
       <c r="Q253" t="inlineStr">
         <is>
           <t>D0=600.47; 最新=2026-06-04; 相对D0=4.81%</t>
@@ -17400,24 +13736,12 @@
       <c r="J254" s="5" t="n">
         <v>30.3</v>
       </c>
-      <c r="K254" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L254" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M254" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N254" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O254" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P254" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K254" s="5" t="n"/>
+      <c r="L254" s="5" t="n"/>
+      <c r="M254" s="5" t="n"/>
+      <c r="N254" s="5" t="n"/>
+      <c r="O254" s="5" t="n"/>
+      <c r="P254" s="5" t="n"/>
       <c r="Q254" s="5" t="inlineStr">
         <is>
           <t>D0=24.86; 最新=2026-06-04; 相对D0=21.88%</t>
@@ -17469,24 +13793,6 @@
       <c r="J255" t="n">
         <v>419.56</v>
       </c>
-      <c r="K255" t="n">
-        <v/>
-      </c>
-      <c r="L255" t="n">
-        <v/>
-      </c>
-      <c r="M255" t="n">
-        <v/>
-      </c>
-      <c r="N255" t="n">
-        <v/>
-      </c>
-      <c r="O255" t="n">
-        <v/>
-      </c>
-      <c r="P255" t="n">
-        <v/>
-      </c>
       <c r="Q255" t="inlineStr">
         <is>
           <t>D0=415.88; 最新=2026-06-04; 相对D0=0.88%</t>
@@ -17538,24 +13844,6 @@
       <c r="J256" t="n">
         <v>43.23</v>
       </c>
-      <c r="K256" t="n">
-        <v/>
-      </c>
-      <c r="L256" t="n">
-        <v/>
-      </c>
-      <c r="M256" t="n">
-        <v/>
-      </c>
-      <c r="N256" t="n">
-        <v/>
-      </c>
-      <c r="O256" t="n">
-        <v/>
-      </c>
-      <c r="P256" t="n">
-        <v/>
-      </c>
       <c r="Q256" t="inlineStr">
         <is>
           <t>D0=44.71; 最新=2026-06-04; 相对D0=-3.31%</t>
@@ -17607,24 +13895,6 @@
       <c r="J257" t="n">
         <v>16.705</v>
       </c>
-      <c r="K257" t="n">
-        <v/>
-      </c>
-      <c r="L257" t="n">
-        <v/>
-      </c>
-      <c r="M257" t="n">
-        <v/>
-      </c>
-      <c r="N257" t="n">
-        <v/>
-      </c>
-      <c r="O257" t="n">
-        <v/>
-      </c>
-      <c r="P257" t="n">
-        <v/>
-      </c>
       <c r="Q257" t="inlineStr">
         <is>
           <t>D0=16.42; 最新=2026-06-04; 相对D0=1.74%</t>
@@ -17676,24 +13946,12 @@
       <c r="J258" s="5" t="n">
         <v>222.325</v>
       </c>
-      <c r="K258" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L258" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M258" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N258" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O258" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P258" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K258" s="5" t="n"/>
+      <c r="L258" s="5" t="n"/>
+      <c r="M258" s="5" t="n"/>
+      <c r="N258" s="5" t="n"/>
+      <c r="O258" s="5" t="n"/>
+      <c r="P258" s="5" t="n"/>
       <c r="Q258" s="5" t="inlineStr">
         <is>
           <t>D0=214.60; 最新=2026-06-04; 相对D0=3.60%</t>
@@ -17745,24 +14003,6 @@
       <c r="J259" t="n">
         <v>108.4</v>
       </c>
-      <c r="K259" t="n">
-        <v/>
-      </c>
-      <c r="L259" t="n">
-        <v/>
-      </c>
-      <c r="M259" t="n">
-        <v/>
-      </c>
-      <c r="N259" t="n">
-        <v/>
-      </c>
-      <c r="O259" t="n">
-        <v/>
-      </c>
-      <c r="P259" t="n">
-        <v/>
-      </c>
       <c r="Q259" t="inlineStr">
         <is>
           <t>D0=110.93; 最新=2026-06-04; 相对D0=-2.28%</t>
@@ -17814,24 +14054,6 @@
       <c r="J260" t="n">
         <v>7.955</v>
       </c>
-      <c r="K260" t="n">
-        <v/>
-      </c>
-      <c r="L260" t="n">
-        <v/>
-      </c>
-      <c r="M260" t="n">
-        <v/>
-      </c>
-      <c r="N260" t="n">
-        <v/>
-      </c>
-      <c r="O260" t="n">
-        <v/>
-      </c>
-      <c r="P260" t="n">
-        <v/>
-      </c>
       <c r="Q260" t="inlineStr">
         <is>
           <t>D0=8.20; 最新=2026-06-04; 相对D0=-2.99%</t>
@@ -17883,24 +14105,6 @@
       <c r="J261" t="n">
         <v>86.58</v>
       </c>
-      <c r="K261" t="n">
-        <v/>
-      </c>
-      <c r="L261" t="n">
-        <v/>
-      </c>
-      <c r="M261" t="n">
-        <v/>
-      </c>
-      <c r="N261" t="n">
-        <v/>
-      </c>
-      <c r="O261" t="n">
-        <v/>
-      </c>
-      <c r="P261" t="n">
-        <v/>
-      </c>
       <c r="Q261" t="inlineStr">
         <is>
           <t>D0=82.85; 最新=2026-06-04; 相对D0=4.50%</t>
@@ -17952,24 +14156,6 @@
       <c r="J262" t="n">
         <v>426.665</v>
       </c>
-      <c r="K262" t="n">
-        <v/>
-      </c>
-      <c r="L262" t="n">
-        <v/>
-      </c>
-      <c r="M262" t="n">
-        <v/>
-      </c>
-      <c r="N262" t="n">
-        <v/>
-      </c>
-      <c r="O262" t="n">
-        <v/>
-      </c>
-      <c r="P262" t="n">
-        <v/>
-      </c>
       <c r="Q262" t="inlineStr">
         <is>
           <t>D0=427.34; 最新=2026-06-04; 相对D0=-0.16%</t>
@@ -18021,24 +14207,12 @@
       <c r="J263" s="5" t="n">
         <v>25.705</v>
       </c>
-      <c r="K263" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L263" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M263" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N263" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O263" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P263" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K263" s="5" t="n"/>
+      <c r="L263" s="5" t="n"/>
+      <c r="M263" s="5" t="n"/>
+      <c r="N263" s="5" t="n"/>
+      <c r="O263" s="5" t="n"/>
+      <c r="P263" s="5" t="n"/>
       <c r="Q263" s="5" t="inlineStr">
         <is>
           <t>D0=26.37; 最新=2026-06-04; 相对D0=-2.52%</t>
@@ -18090,24 +14264,12 @@
       <c r="J264" s="5" t="n">
         <v>65.61</v>
       </c>
-      <c r="K264" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L264" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M264" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N264" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O264" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P264" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K264" s="5" t="n"/>
+      <c r="L264" s="5" t="n"/>
+      <c r="M264" s="5" t="n"/>
+      <c r="N264" s="5" t="n"/>
+      <c r="O264" s="5" t="n"/>
+      <c r="P264" s="5" t="n"/>
       <c r="Q264" s="5" t="inlineStr">
         <is>
           <t>D0=65.21; 最新=2026-06-04; 相对D0=0.61%</t>
@@ -18159,24 +14321,6 @@
       <c r="J265" t="n">
         <v>140.59</v>
       </c>
-      <c r="K265" t="n">
-        <v/>
-      </c>
-      <c r="L265" t="n">
-        <v/>
-      </c>
-      <c r="M265" t="n">
-        <v/>
-      </c>
-      <c r="N265" t="n">
-        <v/>
-      </c>
-      <c r="O265" t="n">
-        <v/>
-      </c>
-      <c r="P265" t="n">
-        <v/>
-      </c>
       <c r="Q265" t="inlineStr">
         <is>
           <t>D0=142.20; 最新=2026-06-04; 相对D0=-1.13%</t>
@@ -18228,24 +14372,6 @@
       <c r="J266" t="n">
         <v>14.72</v>
       </c>
-      <c r="K266" t="n">
-        <v/>
-      </c>
-      <c r="L266" t="n">
-        <v/>
-      </c>
-      <c r="M266" t="n">
-        <v/>
-      </c>
-      <c r="N266" t="n">
-        <v/>
-      </c>
-      <c r="O266" t="n">
-        <v/>
-      </c>
-      <c r="P266" t="n">
-        <v/>
-      </c>
       <c r="Q266" t="inlineStr">
         <is>
           <t>D0=14.85; 最新=2026-06-04; 相对D0=-0.88%</t>
@@ -18297,24 +14423,12 @@
       <c r="J267" s="5" t="n">
         <v>12.0901</v>
       </c>
-      <c r="K267" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L267" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M267" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N267" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O267" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P267" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K267" s="5" t="n"/>
+      <c r="L267" s="5" t="n"/>
+      <c r="M267" s="5" t="n"/>
+      <c r="N267" s="5" t="n"/>
+      <c r="O267" s="5" t="n"/>
+      <c r="P267" s="5" t="n"/>
       <c r="Q267" s="5" t="inlineStr">
         <is>
           <t>D0=12.27; 最新=2026-06-04; 相对D0=-1.47%</t>
@@ -18366,24 +14480,6 @@
       <c r="J268" t="n">
         <v>16.9893</v>
       </c>
-      <c r="K268" t="n">
-        <v/>
-      </c>
-      <c r="L268" t="n">
-        <v/>
-      </c>
-      <c r="M268" t="n">
-        <v/>
-      </c>
-      <c r="N268" t="n">
-        <v/>
-      </c>
-      <c r="O268" t="n">
-        <v/>
-      </c>
-      <c r="P268" t="n">
-        <v/>
-      </c>
       <c r="Q268" t="inlineStr">
         <is>
           <t>D0=16.68; 最新=2026-06-04; 相对D0=1.85%</t>
@@ -18435,24 +14531,12 @@
       <c r="J269" s="5" t="n">
         <v>152.9</v>
       </c>
-      <c r="K269" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L269" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M269" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N269" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O269" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P269" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K269" s="5" t="n"/>
+      <c r="L269" s="5" t="n"/>
+      <c r="M269" s="5" t="n"/>
+      <c r="N269" s="5" t="n"/>
+      <c r="O269" s="5" t="n"/>
+      <c r="P269" s="5" t="n"/>
       <c r="Q269" s="5" t="inlineStr">
         <is>
           <t>D0=153.80; 最新=2026-06-04; 相对D0=-0.59%</t>
@@ -18549,7 +14633,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="278"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18561,7 +14644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -18680,7 +14763,7 @@
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F3" s="11" t="n">
@@ -18938,7 +15021,6 @@
       <c r="F8" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>68.5</v>
       </c>
@@ -19090,7 +15172,6 @@
       <c r="F11" t="n">
         <v>14.7</v>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>14.68</v>
       </c>
@@ -19109,7 +15190,6 @@
       <c r="M11" s="19" t="n">
         <v>0.002041</v>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
@@ -19242,7 +15322,6 @@
       <c r="F14" t="n">
         <v>15.58</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>15.25</v>
       </c>
@@ -19261,7 +15340,6 @@
       <c r="M14" s="20" t="n">
         <v>-0.055751</v>
       </c>
-      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -19417,7 +15495,6 @@
       <c r="M17" s="20" t="n">
         <v>-0.009277000000000001</v>
       </c>
-      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -20026,9 +16103,7 @@
           <t>ASTS</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="15" t="n"/>
       <c r="C36" s="5" t="inlineStr">
         <is>
           <t>17 商业航天</t>
@@ -20074,9 +16149,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="15" t="n"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -20126,9 +16199,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B38" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="15" t="n"/>
       <c r="C38" s="5" t="inlineStr">
         <is>
           <t>15 公用事业</t>
@@ -20174,9 +16245,7 @@
           <t>ENTG</t>
         </is>
       </c>
-      <c r="B39" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B39" s="15" t="n"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -20222,9 +16291,7 @@
           <t>META</t>
         </is>
       </c>
-      <c r="B40" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B40" s="15" t="n"/>
       <c r="C40" s="5" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -20270,9 +16337,7 @@
           <t>NVTS</t>
         </is>
       </c>
-      <c r="B41" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="15" t="n"/>
       <c r="C41" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -20318,9 +16383,7 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B42" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="15" t="n"/>
       <c r="C42" s="5" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -20450,7 +16513,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20462,7 +16524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P44"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -20763,7 +16825,7 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>买入跟踪 | 正式买入 | 第一买入点 | 预警买入</t>
+          <t>买入跟踪 | 正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F6" s="11" t="n">
@@ -21088,7 +17150,6 @@
       <c r="O11" s="20" t="n">
         <v>-0.010408</v>
       </c>
-      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -21291,7 +17352,6 @@
       <c r="F15" t="n">
         <v>1921.71</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>1940.04</v>
       </c>
@@ -21316,7 +17376,6 @@
       <c r="O15" s="19" t="n">
         <v>0.102344</v>
       </c>
-      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16"/>
     <row r="17">
@@ -21579,9 +17638,7 @@
           <t>AEHR</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B27" s="15" t="n"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -21633,9 +17690,7 @@
           <t>AMKR</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B28" s="15" t="n"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -21687,9 +17742,7 @@
           <t>BE</t>
         </is>
       </c>
-      <c r="B29" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B29" s="15" t="n"/>
       <c r="C29" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -21741,9 +17794,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B30" s="15" t="n"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -21799,9 +17850,7 @@
           <t>COHR</t>
         </is>
       </c>
-      <c r="B31" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B31" s="15" t="n"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -21853,9 +17902,7 @@
           <t>FLNC</t>
         </is>
       </c>
-      <c r="B32" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B32" s="15" t="n"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -21907,9 +17954,7 @@
           <t>INTC</t>
         </is>
       </c>
-      <c r="B33" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="15" t="n"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
           <t>03 GPU / AI芯片</t>
@@ -21961,9 +18006,7 @@
           <t>NRG</t>
         </is>
       </c>
-      <c r="B34" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B34" s="15" t="n"/>
       <c r="C34" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -22015,9 +18058,7 @@
           <t>TSEM</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="15" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -22153,7 +18194,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22165,7 +18205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:R44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -22917,7 +18957,6 @@
       <c r="Q12" s="19" t="n">
         <v>0.020981</v>
       </c>
-      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -22946,7 +18985,6 @@
       <c r="F13" t="n">
         <v>290.01</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>285</v>
       </c>
@@ -23045,7 +19083,6 @@
       <c r="Q14" s="19" t="n">
         <v>0.004172</v>
       </c>
-      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -23074,7 +19111,6 @@
       <c r="F15" t="n">
         <v>67.38</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>66.94</v>
       </c>
@@ -23138,7 +19174,6 @@
       <c r="F16" t="n">
         <v>1069.4399</v>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>1068.04</v>
       </c>
@@ -23169,7 +19204,6 @@
       <c r="Q16" s="19" t="n">
         <v>0.011382</v>
       </c>
-      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -23862,9 +19896,7 @@
           <t>AXTI</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="15" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -23922,9 +19954,7 @@
           <t>CEG</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="15" t="n"/>
       <c r="C36" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -23982,9 +20012,7 @@
           <t>GLW</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="15" t="n"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -24042,9 +20070,7 @@
           <t>SNPS</t>
         </is>
       </c>
-      <c r="B38" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="15" t="n"/>
       <c r="C38" s="5" t="inlineStr">
         <is>
           <t>04 半导体设备 / EDA</t>
@@ -24160,9 +20186,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24174,7 +20197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T36"/>
+  <dimension ref="A1:T32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -24469,7 +20492,7 @@
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点</t>
+          <t>正式买入 | 第一观察点</t>
         </is>
       </c>
       <c r="F5" s="11" t="n">
@@ -24535,7 +20558,7 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F6" s="11" t="n">
@@ -24751,7 +20774,6 @@
       <c r="F9" t="n">
         <v>190.96</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>203.7</v>
       </c>
@@ -24788,7 +20810,6 @@
       <c r="S9" s="19" t="n">
         <v>0.22544</v>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -24817,7 +20838,6 @@
       <c r="F10" t="n">
         <v>90.87</v>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>91.09</v>
       </c>
@@ -24998,7 +21018,6 @@
       <c r="S12" s="19" t="n">
         <v>0.03633</v>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -25417,9 +21436,7 @@
           <t>SLB</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B26" s="15" t="n"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -25483,9 +21500,7 @@
           <t>ZS</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B27" s="15" t="n"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -25594,10 +21609,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25609,7 +21620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V56"/>
+  <dimension ref="A1:V54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -26080,7 +22091,7 @@
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F7" s="11" t="n">
@@ -26238,7 +22249,6 @@
       <c r="F9" t="n">
         <v>105.89</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>104.27</v>
       </c>
@@ -27512,7 +23522,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -27565,7 +23575,6 @@
       <c r="U26" s="19" t="n">
         <v>0.001768</v>
       </c>
-      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -27588,7 +23597,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
@@ -27732,7 +23741,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
@@ -28078,9 +24087,7 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="B41" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="15" t="n"/>
       <c r="C41" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -28150,9 +24157,7 @@
           <t>CVX</t>
         </is>
       </c>
-      <c r="B42" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="15" t="n"/>
       <c r="C42" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -28222,9 +24227,7 @@
           <t>EOG</t>
         </is>
       </c>
-      <c r="B43" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B43" s="15" t="n"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -28294,9 +24297,7 @@
           <t>MDB</t>
         </is>
       </c>
-      <c r="B44" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B44" s="15" t="n"/>
       <c r="C44" s="5" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -28366,9 +24367,7 @@
           <t>OXY</t>
         </is>
       </c>
-      <c r="B45" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="15" t="n"/>
       <c r="C45" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -28438,9 +24437,7 @@
           <t>POET</t>
         </is>
       </c>
-      <c r="B46" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B46" s="15" t="n"/>
       <c r="C46" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -28510,9 +24507,7 @@
           <t>XLE</t>
         </is>
       </c>
-      <c r="B47" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B47" s="15" t="n"/>
       <c r="C47" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -28653,8 +24648,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28666,7 +24659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -28827,24 +24820,12 @@
       <c r="J3" s="5" t="n">
         <v>181.49</v>
       </c>
-      <c r="K3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
       <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -28896,24 +24877,12 @@
       <c r="J4" s="5" t="n">
         <v>202.91</v>
       </c>
-      <c r="K4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
       <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -28965,24 +24934,12 @@
       <c r="J5" s="5" t="n">
         <v>167.37</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29034,24 +24991,12 @@
       <c r="J6" s="5" t="n">
         <v>46.53</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29103,24 +25048,6 @@
       <c r="J7" t="n">
         <v>16.12</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29172,24 +25099,12 @@
       <c r="J8" s="5" t="n">
         <v>180.07</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29241,24 +25156,12 @@
       <c r="J9" s="5" t="n">
         <v>48.12</v>
       </c>
-      <c r="K9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
       <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29310,24 +25213,6 @@
       <c r="J10" t="n">
         <v>141.22</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29379,24 +25264,12 @@
       <c r="J11" s="5" t="n">
         <v>391.35</v>
       </c>
-      <c r="K11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
       <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29448,24 +25321,12 @@
       <c r="J12" s="5" t="n">
         <v>1038.74</v>
       </c>
-      <c r="K12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
       <c r="Q12" s="5" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29517,24 +25378,12 @@
       <c r="J13" s="5" t="n">
         <v>179.36</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29586,24 +25435,12 @@
       <c r="J14" s="5" t="n">
         <v>326.13</v>
       </c>
-      <c r="K14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29655,24 +25492,6 @@
       <c r="J15" t="n">
         <v>22.51</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29724,24 +25543,6 @@
       <c r="J16" t="n">
         <v>232</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29793,24 +25594,6 @@
       <c r="J17" t="n">
         <v>130.5</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29862,24 +25645,12 @@
       <c r="J18" s="5" t="n">
         <v>262.25</v>
       </c>
-      <c r="K18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -29931,24 +25702,12 @@
       <c r="J19" s="5" t="n">
         <v>85.42</v>
       </c>
-      <c r="K19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -30000,24 +25759,6 @@
       <c r="J20" t="n">
         <v>426.01</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -30069,24 +25810,12 @@
       <c r="J21" s="5" t="n">
         <v>13.02</v>
       </c>
-      <c r="K21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -30323,24 +26052,12 @@
       <c r="J33" s="5" t="n">
         <v>41.47</v>
       </c>
-      <c r="K33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -30385,11 +26102,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30401,7 +26113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X54"/>
+  <dimension ref="A1:X49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -30586,7 +26298,6 @@
       <c r="F3" t="n">
         <v>22.51</v>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>22.62</v>
       </c>
@@ -31078,7 +26789,6 @@
       <c r="F9" t="n">
         <v>181.49</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>177.62</v>
       </c>
@@ -31570,7 +27280,6 @@
       <c r="F15" t="n">
         <v>16.12</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>15.47</v>
       </c>
@@ -31734,7 +27443,6 @@
       <c r="F17" t="n">
         <v>610.26</v>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>612.34</v>
       </c>
@@ -32140,7 +27848,6 @@
       <c r="F22" t="n">
         <v>141.22</v>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>136.2</v>
       </c>
@@ -32222,7 +27929,6 @@
       <c r="F23" t="n">
         <v>58.81</v>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>57.46</v>
       </c>
@@ -32304,7 +28010,6 @@
       <c r="F24" t="n">
         <v>81.76000000000001</v>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>84.64</v>
       </c>
@@ -32380,7 +28085,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
@@ -32468,7 +28173,6 @@
       <c r="F26" t="n">
         <v>426.01</v>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>433.59</v>
       </c>
@@ -32517,7 +28221,6 @@
       <c r="W26" s="20" t="n">
         <v>-0.015516</v>
       </c>
-      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -32540,7 +28243,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
@@ -32868,7 +28571,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
@@ -32950,7 +28653,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
@@ -33386,9 +29089,7 @@
           <t>HAL</t>
         </is>
       </c>
-      <c r="B45" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="15" t="n"/>
       <c r="C45" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -33496,11 +29197,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33808,7 +29504,6 @@
       <c r="V3" t="n">
         <v>177.4799957275391</v>
       </c>
-      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=56.52; 4H分金=43.56</t>
@@ -33934,7 +29629,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -34166,7 +29861,6 @@
       <c r="V7" t="n">
         <v>495</v>
       </c>
-      <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-03; 1出价格=495.00; Gann0=405.86; 段涨幅=21.96%</t>
@@ -34254,7 +29948,6 @@
       <c r="V8" t="n">
         <v>495</v>
       </c>
-      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=41.45; 4H分金=27.45</t>
@@ -34522,7 +30215,6 @@
       <c r="V11" t="n">
         <v>93.69999694824219</v>
       </c>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=93.70; Gann0=80.98; 段涨幅=15.71%</t>
@@ -34610,7 +30302,6 @@
       <c r="V12" t="n">
         <v>93.69999694824219</v>
       </c>
-      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=52.01; 4H分金=37.57</t>
@@ -34788,7 +30479,6 @@
       <c r="V14" t="n">
         <v>94.39499664306641</v>
       </c>
-      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=64.19; 4H分金=50.10</t>
@@ -34876,7 +30566,6 @@
       <c r="V15" t="n">
         <v>474.0299987792969</v>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=57.79; 4H分金=50.60</t>
@@ -35234,7 +30923,6 @@
       <c r="V19" t="n">
         <v>785.6599731445312</v>
       </c>
-      <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=57.12; 4H分金=39.94</t>
@@ -35496,8 +31184,6 @@
       <c r="T22" t="b">
         <v>0</v>
       </c>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
       <c r="W22" t="n">
         <v>88</v>
       </c>
@@ -35948,7 +31634,6 @@
       <c r="V27" t="n">
         <v>332.4599914550781</v>
       </c>
-      <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=64.52; 4H分金=52.01</t>
@@ -36306,7 +31991,6 @@
       <c r="V31" t="n">
         <v>70.70700073242188</v>
       </c>
-      <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-03; 1出价格=70.71; Gann0=46.00; 段涨幅=53.71%</t>
@@ -36394,7 +32078,6 @@
       <c r="V32" t="n">
         <v>70.70700073242188</v>
       </c>
-      <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=51.03; 4H分金=36.71</t>
@@ -36482,7 +32165,6 @@
       <c r="V33" t="n">
         <v>1049.530029296875</v>
       </c>
-      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.22; 4H分金=48.34</t>
@@ -36660,7 +32342,6 @@
       <c r="V35" t="n">
         <v>24.5</v>
       </c>
-      <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-29; 1出价格=24.50; Gann0=20.89; 段涨幅=17.28%</t>
@@ -37018,7 +32699,6 @@
       <c r="V39" t="n">
         <v>60.5</v>
       </c>
-      <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.79; 4H分金=46.29</t>
@@ -37106,7 +32786,6 @@
       <c r="V40" t="n">
         <v>112.2099990844727</v>
       </c>
-      <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=112.21; Gann0=103.14; 段涨幅=8.79%</t>
@@ -37374,7 +33053,6 @@
       <c r="V43" t="n">
         <v>89.72000122070312</v>
       </c>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=51.12; 4H分金=44.11</t>
@@ -37462,7 +33140,6 @@
       <c r="V44" t="n">
         <v>394.6300048828125</v>
       </c>
-      <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=394.63; Gann0=309.36; 段涨幅=27.56%</t>
@@ -37820,7 +33497,6 @@
       <c r="V48" t="n">
         <v>345.1799926757812</v>
       </c>
-      <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=43.54; 4H分金=37.34</t>
@@ -38213,7 +33889,6 @@
       <c r="D3" s="8" t="n">
         <v>46168</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="8" t="n">
         <v>46168</v>
       </c>
@@ -38262,7 +33937,6 @@
           <t>18 化肥</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" s="8" t="n">
         <v>46164</v>
       </c>
@@ -38371,7 +34045,6 @@
       <c r="D6" s="8" t="n">
         <v>46175</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" s="8" t="n">
         <v>46175</v>
       </c>
@@ -38531,7 +34204,6 @@
       <c r="D9" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="8" t="n">
         <v>46174</v>
       </c>
@@ -38691,7 +34363,6 @@
       <c r="D12" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" s="8" t="n">
         <v>46164</v>
       </c>
@@ -38743,7 +34414,6 @@
       <c r="D13" s="8" t="n">
         <v>46168</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="8" t="n">
         <v>46168</v>
       </c>
@@ -38795,7 +34465,6 @@
       <c r="D14" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" s="8" t="n">
         <v>46174</v>
       </c>
@@ -38847,7 +34516,6 @@
       <c r="D15" s="8" t="n">
         <v>46175</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" s="8" t="n">
         <v>46175</v>
       </c>
@@ -38953,7 +34621,6 @@
       <c r="D17" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" s="8" t="n">
         <v>46174</v>
       </c>
@@ -39005,7 +34672,6 @@
       <c r="D18" s="8" t="n">
         <v>46168</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" s="8" t="n">
         <v>46168</v>
       </c>
@@ -39111,7 +34777,6 @@
       <c r="D20" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" s="8" t="n">
         <v>46164</v>
       </c>
@@ -39163,7 +34828,6 @@
       <c r="D21" s="8" t="n">
         <v>46175</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" s="8" t="n">
         <v>46175</v>
       </c>
@@ -39212,7 +34876,6 @@
           <t>19 COWOS</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" s="8" t="n">
         <v>46164</v>
       </c>
@@ -39321,7 +34984,6 @@
       <c r="D24" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" s="8" t="n">
         <v>46164</v>
       </c>
@@ -39481,7 +35143,6 @@
       <c r="D27" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" s="8" t="n">
         <v>46164</v>
       </c>
@@ -39801,7 +35462,6 @@
       <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" s="8" t="n">
         <v>46177</v>
       </c>
@@ -40483,7 +36143,6 @@
       <c r="I16" t="n">
         <v>3</v>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" s="8" t="n">
         <v>46175</v>
       </c>
@@ -41165,7 +36824,6 @@
       <c r="I28" t="n">
         <v>5</v>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" s="8" t="n">
         <v>46171</v>
       </c>
@@ -41277,7 +36935,6 @@
       <c r="I30" t="n">
         <v>7</v>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" s="8" t="n">
         <v>46169</v>
       </c>
@@ -41309,7 +36966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -41494,7 +37151,7 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F6" s="11" t="n">
@@ -41607,7 +37264,6 @@
           <t>2026-05-22 (98), 2026-05-26 (100), 2026-05-29 (98), 2026-06-02 (95)</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -41641,7 +37297,6 @@
           <t>2026-05-22 (90), 2026-05-27 (100)</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -42227,9 +37882,7 @@
           <t>AVGO</t>
         </is>
       </c>
-      <c r="B34" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B34" s="15" t="n"/>
       <c r="C34" s="5" t="inlineStr">
         <is>
           <t>03 GPU / AI芯片</t>
@@ -42257,9 +37910,7 @@
           <t>BHP</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="15" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>13 材料 / 电网</t>
@@ -42287,9 +37938,7 @@
           <t>IREN</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="15" t="n"/>
       <c r="C36" s="5" t="inlineStr">
         <is>
           <t>21 数据中心</t>
@@ -42317,9 +37966,7 @@
           <t>MOS</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="15" t="n"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
           <t>18 农业/化肥</t>
@@ -42347,9 +37994,7 @@
           <t>RIO</t>
         </is>
       </c>
-      <c r="B38" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="15" t="n"/>
       <c r="C38" s="5" t="inlineStr">
         <is>
           <t>13 材料 / 电网</t>
@@ -42377,9 +38022,7 @@
           <t>TLN</t>
         </is>
       </c>
-      <c r="B39" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B39" s="15" t="n"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -42491,7 +38134,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -42503,7 +38145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -42916,14 +38558,12 @@
       <c r="F11" t="n">
         <v>43.71</v>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>43.825</v>
       </c>
       <c r="I11" s="19" t="n">
         <v>0.002631</v>
       </c>
-      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -42992,14 +38632,12 @@
       <c r="F13" t="n">
         <v>282.27</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>284.365</v>
       </c>
       <c r="I13" s="19" t="n">
         <v>0.007422</v>
       </c>
-      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -43119,7 +38757,6 @@
       <c r="I16" s="19" t="n">
         <v>0.079663</v>
       </c>
-      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -43159,7 +38796,6 @@
       <c r="I17" s="20" t="n">
         <v>-0.014307</v>
       </c>
-      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
@@ -43235,7 +38871,6 @@
       <c r="I19" s="19" t="n">
         <v>0.01403</v>
       </c>
-      <c r="J19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -43275,7 +38910,6 @@
       <c r="I20" s="20" t="n">
         <v>-0.012336</v>
       </c>
-      <c r="J20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -43298,7 +38932,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F21" s="5" t="n">
@@ -43395,7 +39029,6 @@
       <c r="I23" s="20" t="n">
         <v>-0.017348</v>
       </c>
-      <c r="J23" t="inlineStr"/>
     </row>
     <row r="24"/>
     <row r="25">
@@ -43617,9 +39250,7 @@
           <t>APLD</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="15" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>21 数据中心</t>
@@ -43653,9 +39284,7 @@
           <t>CPNG</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="15" t="n"/>
       <c r="C36" s="5" t="inlineStr">
         <is>
           <t>23 杂项</t>
@@ -43689,9 +39318,7 @@
           <t>CRDO</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="15" t="n"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -43725,9 +39352,7 @@
           <t>CRWV</t>
         </is>
       </c>
-      <c r="B38" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="15" t="n"/>
       <c r="C38" s="5" t="inlineStr">
         <is>
           <t>21 数据中心</t>
@@ -43761,9 +39386,7 @@
           <t>EOSE</t>
         </is>
       </c>
-      <c r="B39" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B39" s="21" t="n"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -43782,14 +39405,12 @@
       <c r="F39" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>7.955</v>
       </c>
       <c r="I39" s="20" t="n">
         <v>-0.029878</v>
       </c>
-      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -43797,9 +39418,7 @@
           <t>HOOD</t>
         </is>
       </c>
-      <c r="B40" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B40" s="15" t="n"/>
       <c r="C40" s="5" t="inlineStr">
         <is>
           <t>16 金融股</t>
@@ -43833,9 +39452,7 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B41" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="21" t="n"/>
       <c r="C41" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -43854,14 +39471,12 @@
       <c r="F41" t="n">
         <v>427.34</v>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>426.665</v>
       </c>
       <c r="I41" s="20" t="n">
         <v>-0.00158</v>
       </c>
-      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
@@ -43869,9 +39484,7 @@
           <t>NNE</t>
         </is>
       </c>
-      <c r="B42" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="15" t="n"/>
       <c r="C42" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -43905,9 +39518,7 @@
           <t>OKLO</t>
         </is>
       </c>
-      <c r="B43" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B43" s="15" t="n"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -43941,9 +39552,7 @@
           <t>PLTR</t>
         </is>
       </c>
-      <c r="B44" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B44" s="21" t="n"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -43962,14 +39571,12 @@
       <c r="F44" t="n">
         <v>142.2</v>
       </c>
-      <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
         <v>140.59</v>
       </c>
       <c r="I44" s="20" t="n">
         <v>-0.011322</v>
       </c>
-      <c r="J44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -43977,9 +39584,7 @@
           <t>RUN</t>
         </is>
       </c>
-      <c r="B45" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="21" t="n"/>
       <c r="C45" t="inlineStr">
         <is>
           <t>10 太阳能</t>
@@ -43998,14 +39603,12 @@
       <c r="F45" t="n">
         <v>14.85</v>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
         <v>14.72</v>
       </c>
       <c r="I45" s="20" t="n">
         <v>-0.008754</v>
       </c>
-      <c r="J45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -44013,9 +39616,7 @@
           <t>SMR</t>
         </is>
       </c>
-      <c r="B46" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B46" s="15" t="n"/>
       <c r="C46" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -44049,9 +39650,7 @@
           <t>SOFI</t>
         </is>
       </c>
-      <c r="B47" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B47" s="15" t="n"/>
       <c r="C47" s="5" t="inlineStr">
         <is>
           <t>16 金融股</t>
@@ -44085,9 +39684,7 @@
           <t>VST</t>
         </is>
       </c>
-      <c r="B48" s="21" t="n">
-        <v/>
-      </c>
+      <c r="B48" s="21" t="n"/>
       <c r="C48" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -44106,14 +39703,12 @@
       <c r="F48" t="n">
         <v>153.8</v>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
         <v>152.9</v>
       </c>
       <c r="I48" s="20" t="n">
         <v>-0.005852</v>
       </c>
-      <c r="J48" t="inlineStr"/>
     </row>
     <row r="49"/>
     <row r="50">
@@ -44205,7 +39800,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -44485,7 +40079,6 @@
       <c r="K6" s="20" t="n">
         <v>-0.027468</v>
       </c>
-      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -44600,7 +40193,7 @@
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F9" s="11" t="n">
@@ -44646,7 +40239,7 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F10" s="11" t="n">
@@ -44692,7 +40285,7 @@
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点</t>
+          <t>正式买入 | 第一观察点</t>
         </is>
       </c>
       <c r="F11" s="11" t="n">
@@ -45661,7 +41254,6 @@
       <c r="K32" s="19" t="n">
         <v>0.002232</v>
       </c>
-      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -45799,7 +41391,6 @@
       <c r="K35" s="19" t="n">
         <v>0.010195</v>
       </c>
-      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -45845,7 +41436,6 @@
       <c r="K36" s="20" t="n">
         <v>-0.028321</v>
       </c>
-      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -45962,7 +41552,6 @@
       <c r="F39" t="n">
         <v>315.2</v>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>310.26</v>
       </c>
@@ -46008,7 +41597,6 @@
       <c r="F40" t="n">
         <v>72.33</v>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>69.02</v>
       </c>
@@ -46021,7 +41609,6 @@
       <c r="K40" s="20" t="n">
         <v>-0.052468</v>
       </c>
-      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -46050,7 +41637,6 @@
       <c r="F41" t="n">
         <v>11.72</v>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>11.1</v>
       </c>
@@ -46063,7 +41649,6 @@
       <c r="K41" s="20" t="n">
         <v>-0.036689</v>
       </c>
-      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42"/>
     <row r="43">
